--- a/research/traditional_assets/database/data/panama/panama_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/panama/panama_real_estate_operations_services.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08594289142111586</v>
+        <v>0.08576178419256307</v>
       </c>
       <c r="C2">
-        <v>7239.723020593662</v>
+        <v>7202.107026725502</v>
       </c>
       <c r="D2">
-        <v>6979.023020593662</v>
+        <v>7010.652026725502</v>
       </c>
       <c r="E2">
-        <v>-6691.7</v>
+        <v>-6622.455</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>69.245</v>
       </c>
       <c r="G2">
         <v>260.7</v>
@@ -1439,28 +1439,28 @@
         <v>452.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.4830235</v>
       </c>
       <c r="N2">
-        <v>452.5</v>
+        <v>449.0169765</v>
       </c>
       <c r="O2">
-        <v>113.125</v>
+        <v>112.254244125</v>
       </c>
       <c r="P2">
-        <v>339.375</v>
+        <v>336.762732375</v>
       </c>
       <c r="Q2">
-        <v>346.375</v>
+        <v>343.762732375</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08594289142111586</v>
+        <v>0.0862470042349122</v>
       </c>
       <c r="T2">
-        <v>0.5525820103960151</v>
+        <v>0.5567682377475001</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>129.9158618941273</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08576178419256307</v>
+        <v>0.0855806769640103</v>
       </c>
       <c r="C3">
-        <v>7202.107026725502</v>
+        <v>7164.779024016846</v>
       </c>
       <c r="D3">
-        <v>7010.652026725502</v>
+        <v>7042.569024016846</v>
       </c>
       <c r="E3">
-        <v>-6622.455</v>
+        <v>-6553.21</v>
       </c>
       <c r="F3">
-        <v>69.245</v>
+        <v>138.49</v>
       </c>
       <c r="G3">
         <v>260.7</v>
@@ -1521,28 +1521,28 @@
         <v>452.5</v>
       </c>
       <c r="M3">
-        <v>3.4830235</v>
+        <v>6.966047000000001</v>
       </c>
       <c r="N3">
-        <v>449.0169765</v>
+        <v>445.533953</v>
       </c>
       <c r="O3">
-        <v>112.254244125</v>
+        <v>111.38348825</v>
       </c>
       <c r="P3">
-        <v>336.762732375</v>
+        <v>334.15046475</v>
       </c>
       <c r="Q3">
-        <v>343.762732375</v>
+        <v>341.15046475</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0862470042349122</v>
+        <v>0.08655732343266356</v>
       </c>
       <c r="T3">
-        <v>0.5567682377475001</v>
+        <v>0.5610398983102398</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>129.9158618941273</v>
+        <v>64.95793094706366</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0855806769640103</v>
+        <v>0.0853995697354575</v>
       </c>
       <c r="C4">
-        <v>7164.779024016846</v>
+        <v>7127.742963819782</v>
       </c>
       <c r="D4">
-        <v>7042.569024016846</v>
+        <v>7074.777963819782</v>
       </c>
       <c r="E4">
-        <v>-6553.21</v>
+        <v>-6483.965</v>
       </c>
       <c r="F4">
-        <v>138.49</v>
+        <v>207.735</v>
       </c>
       <c r="G4">
         <v>260.7</v>
@@ -1603,28 +1603,28 @@
         <v>452.5</v>
       </c>
       <c r="M4">
-        <v>6.966047000000001</v>
+        <v>10.4490705</v>
       </c>
       <c r="N4">
-        <v>445.533953</v>
+        <v>442.0509295</v>
       </c>
       <c r="O4">
-        <v>111.38348825</v>
+        <v>110.512732375</v>
       </c>
       <c r="P4">
-        <v>334.15046475</v>
+        <v>331.538197125</v>
       </c>
       <c r="Q4">
-        <v>341.15046475</v>
+        <v>338.538197125</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08655732343266356</v>
+        <v>0.08687404096438917</v>
       </c>
       <c r="T4">
-        <v>0.5610398983102398</v>
+        <v>0.5653996343484999</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>64.95793094706366</v>
+        <v>43.30528729804244</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0853995697354575</v>
+        <v>0.08521846250690469</v>
       </c>
       <c r="C5">
-        <v>7127.742963819782</v>
+        <v>7091.002870103972</v>
       </c>
       <c r="D5">
-        <v>7074.777963819782</v>
+        <v>7107.282870103973</v>
       </c>
       <c r="E5">
-        <v>-6483.965</v>
+        <v>-6414.719999999999</v>
       </c>
       <c r="F5">
-        <v>207.735</v>
+        <v>276.98</v>
       </c>
       <c r="G5">
         <v>260.7</v>
@@ -1685,28 +1685,28 @@
         <v>452.5</v>
       </c>
       <c r="M5">
-        <v>10.4490705</v>
+        <v>13.932094</v>
       </c>
       <c r="N5">
-        <v>442.0509295</v>
+        <v>438.567906</v>
       </c>
       <c r="O5">
-        <v>110.512732375</v>
+        <v>109.6419765</v>
       </c>
       <c r="P5">
-        <v>331.538197125</v>
+        <v>328.9259295</v>
       </c>
       <c r="Q5">
-        <v>338.538197125</v>
+        <v>335.9259295</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08687404096438917</v>
+        <v>0.08719735677802573</v>
       </c>
       <c r="T5">
-        <v>0.5653996343484999</v>
+        <v>0.5698501982208906</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>43.30528729804244</v>
+        <v>32.47896547353183</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08521846250690469</v>
+        <v>0.08503735527835192</v>
       </c>
       <c r="C6">
-        <v>7091.002870103972</v>
+        <v>7054.56284113257</v>
       </c>
       <c r="D6">
-        <v>7107.282870103973</v>
+        <v>7140.08784113257</v>
       </c>
       <c r="E6">
-        <v>-6414.719999999999</v>
+        <v>-6345.474999999999</v>
       </c>
       <c r="F6">
-        <v>276.98</v>
+        <v>346.225</v>
       </c>
       <c r="G6">
         <v>260.7</v>
@@ -1767,28 +1767,28 @@
         <v>452.5</v>
       </c>
       <c r="M6">
-        <v>13.932094</v>
+        <v>17.4151175</v>
       </c>
       <c r="N6">
-        <v>438.567906</v>
+        <v>435.0848825</v>
       </c>
       <c r="O6">
-        <v>109.6419765</v>
+        <v>108.771220625</v>
       </c>
       <c r="P6">
-        <v>328.9259295</v>
+        <v>326.313661875</v>
       </c>
       <c r="Q6">
-        <v>335.9259295</v>
+        <v>333.313661875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08719735677802573</v>
+        <v>0.08752747924037044</v>
       </c>
       <c r="T6">
-        <v>0.5698501982208906</v>
+        <v>0.5743944581748052</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.47896547353183</v>
+        <v>25.98317237882546</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08503735527835192</v>
+        <v>0.08485624804979913</v>
       </c>
       <c r="C7">
-        <v>7054.56284113257</v>
+        <v>7018.427051184754</v>
       </c>
       <c r="D7">
-        <v>7140.08784113257</v>
+        <v>7173.197051184755</v>
       </c>
       <c r="E7">
-        <v>-6345.474999999999</v>
+        <v>-6276.23</v>
       </c>
       <c r="F7">
-        <v>346.225</v>
+        <v>415.47</v>
       </c>
       <c r="G7">
         <v>260.7</v>
@@ -1849,28 +1849,28 @@
         <v>452.5</v>
       </c>
       <c r="M7">
-        <v>17.4151175</v>
+        <v>20.898141</v>
       </c>
       <c r="N7">
-        <v>435.0848825</v>
+        <v>431.601859</v>
       </c>
       <c r="O7">
-        <v>108.771220625</v>
+        <v>107.90046475</v>
       </c>
       <c r="P7">
-        <v>326.313661875</v>
+        <v>323.70139425</v>
       </c>
       <c r="Q7">
-        <v>333.313661875</v>
+        <v>330.70139425</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08752747924037044</v>
+        <v>0.08786462558489269</v>
       </c>
       <c r="T7">
-        <v>0.5743944581748052</v>
+        <v>0.5790354045107179</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.98317237882546</v>
+        <v>21.65264364902122</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08485624804979913</v>
+        <v>0.08467514082124633</v>
       </c>
       <c r="C8">
-        <v>7018.427051184754</v>
+        <v>6982.599752326383</v>
       </c>
       <c r="D8">
-        <v>7173.197051184755</v>
+        <v>7206.614752326383</v>
       </c>
       <c r="E8">
-        <v>-6276.23</v>
+        <v>-6206.985</v>
       </c>
       <c r="F8">
-        <v>415.47</v>
+        <v>484.715</v>
       </c>
       <c r="G8">
         <v>260.7</v>
@@ -1931,28 +1931,28 @@
         <v>452.5</v>
       </c>
       <c r="M8">
-        <v>20.898141</v>
+        <v>24.3811645</v>
       </c>
       <c r="N8">
-        <v>431.601859</v>
+        <v>428.1188355</v>
       </c>
       <c r="O8">
-        <v>107.90046475</v>
+        <v>107.029708875</v>
       </c>
       <c r="P8">
-        <v>323.70139425</v>
+        <v>321.089126625</v>
       </c>
       <c r="Q8">
-        <v>330.70139425</v>
+        <v>328.089126625</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08786462558489269</v>
+        <v>0.08820902238843692</v>
       </c>
       <c r="T8">
-        <v>0.5790354045107179</v>
+        <v>0.5837761561441772</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.65264364902122</v>
+        <v>18.55940884201819</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08467514082124633</v>
+        <v>0.08449403359269356</v>
       </c>
       <c r="C9">
-        <v>6982.599752326383</v>
+        <v>6947.085276230406</v>
       </c>
       <c r="D9">
-        <v>7206.614752326383</v>
+        <v>7240.345276230406</v>
       </c>
       <c r="E9">
-        <v>-6206.985</v>
+        <v>-6137.74</v>
       </c>
       <c r="F9">
-        <v>484.715</v>
+        <v>553.96</v>
       </c>
       <c r="G9">
         <v>260.7</v>
@@ -2013,28 +2013,28 @@
         <v>452.5</v>
       </c>
       <c r="M9">
-        <v>24.3811645</v>
+        <v>27.864188</v>
       </c>
       <c r="N9">
-        <v>428.1188355</v>
+        <v>424.635812</v>
       </c>
       <c r="O9">
-        <v>107.029708875</v>
+        <v>106.158953</v>
       </c>
       <c r="P9">
-        <v>321.089126625</v>
+        <v>318.476859</v>
       </c>
       <c r="Q9">
-        <v>328.089126625</v>
+        <v>325.476859</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08820902238843692</v>
+        <v>0.08856090607901473</v>
       </c>
       <c r="T9">
-        <v>0.5837761561441772</v>
+        <v>0.5886199675957552</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.55940884201819</v>
+        <v>16.23948273676591</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08449403359269356</v>
+        <v>0.08431292636414077</v>
       </c>
       <c r="C10">
-        <v>6947.085276230406</v>
+        <v>6911.888036048634</v>
       </c>
       <c r="D10">
-        <v>7240.345276230406</v>
+        <v>7274.393036048634</v>
       </c>
       <c r="E10">
-        <v>-6137.74</v>
+        <v>-6068.495</v>
       </c>
       <c r="F10">
-        <v>553.96</v>
+        <v>623.2049999999999</v>
       </c>
       <c r="G10">
         <v>260.7</v>
@@ -2095,28 +2095,28 @@
         <v>452.5</v>
       </c>
       <c r="M10">
-        <v>27.864188</v>
+        <v>31.34721149999999</v>
       </c>
       <c r="N10">
-        <v>424.635812</v>
+        <v>421.1527885</v>
       </c>
       <c r="O10">
-        <v>106.158953</v>
+        <v>105.288197125</v>
       </c>
       <c r="P10">
-        <v>318.476859</v>
+        <v>315.864591375</v>
       </c>
       <c r="Q10">
-        <v>325.476859</v>
+        <v>322.864591375</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08856090607901473</v>
+        <v>0.08892052347707777</v>
       </c>
       <c r="T10">
-        <v>0.5886199675957552</v>
+        <v>0.5935702364418733</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.23948273676591</v>
+        <v>14.43509576601415</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08431292636414077</v>
+        <v>0.08413181913558797</v>
       </c>
       <c r="C11">
-        <v>6911.888036048634</v>
+        <v>6877.012528336554</v>
       </c>
       <c r="D11">
-        <v>7274.393036048634</v>
+        <v>7308.762528336554</v>
       </c>
       <c r="E11">
-        <v>-6068.495</v>
+        <v>-5999.25</v>
       </c>
       <c r="F11">
-        <v>623.2049999999999</v>
+        <v>692.4499999999999</v>
       </c>
       <c r="G11">
         <v>260.7</v>
@@ -2177,28 +2177,28 @@
         <v>452.5</v>
       </c>
       <c r="M11">
-        <v>31.34721149999999</v>
+        <v>34.83023499999999</v>
       </c>
       <c r="N11">
-        <v>421.1527885</v>
+        <v>417.669765</v>
       </c>
       <c r="O11">
-        <v>105.288197125</v>
+        <v>104.41744125</v>
       </c>
       <c r="P11">
-        <v>315.864591375</v>
+        <v>313.25232375</v>
       </c>
       <c r="Q11">
-        <v>322.864591375</v>
+        <v>320.25232375</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08892052347707777</v>
+        <v>0.08928813237287551</v>
       </c>
       <c r="T11">
-        <v>0.5935702364418733</v>
+        <v>0.5986305112623496</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.43509576601415</v>
+        <v>12.99158618941273</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08413181913558797</v>
+        <v>0.08407446190703517</v>
       </c>
       <c r="C12">
-        <v>6877.012528336554</v>
+        <v>6818.720271808015</v>
       </c>
       <c r="D12">
-        <v>7308.762528336554</v>
+        <v>7319.715271808015</v>
       </c>
       <c r="E12">
-        <v>-5999.25</v>
+        <v>-5930.005</v>
       </c>
       <c r="F12">
-        <v>692.45</v>
+        <v>761.6950000000001</v>
       </c>
       <c r="G12">
         <v>260.7</v>
@@ -2259,45 +2259,45 @@
         <v>452.5</v>
       </c>
       <c r="M12">
-        <v>34.830235</v>
+        <v>39.455801</v>
       </c>
       <c r="N12">
-        <v>417.669765</v>
+        <v>413.044199</v>
       </c>
       <c r="O12">
-        <v>104.41744125</v>
+        <v>103.26104975</v>
       </c>
       <c r="P12">
-        <v>313.25232375</v>
+        <v>309.78314925</v>
       </c>
       <c r="Q12">
-        <v>320.25232375</v>
+        <v>316.78314925</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08928813237287551</v>
+        <v>0.08966400214273615</v>
       </c>
       <c r="T12">
-        <v>0.5986305112623496</v>
+        <v>0.6038045001237355</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>12.99158618941273</v>
+        <v>11.46852905102598</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08407446190703517</v>
+        <v>0.08390460467848239</v>
       </c>
       <c r="C13">
-        <v>6818.720271808015</v>
+        <v>6782.10404621351</v>
       </c>
       <c r="D13">
-        <v>7319.715271808015</v>
+        <v>7352.34404621351</v>
       </c>
       <c r="E13">
-        <v>-5930.005</v>
+        <v>-5860.76</v>
       </c>
       <c r="F13">
-        <v>761.6950000000001</v>
+        <v>830.9399999999999</v>
       </c>
       <c r="G13">
         <v>260.7</v>
@@ -2341,28 +2341,28 @@
         <v>452.5</v>
       </c>
       <c r="M13">
-        <v>39.455801</v>
+        <v>43.042692</v>
       </c>
       <c r="N13">
-        <v>413.044199</v>
+        <v>409.457308</v>
       </c>
       <c r="O13">
-        <v>103.26104975</v>
+        <v>102.364327</v>
       </c>
       <c r="P13">
-        <v>309.78314925</v>
+        <v>307.092981</v>
       </c>
       <c r="Q13">
-        <v>316.78314925</v>
+        <v>314.092981</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08966400214273615</v>
+        <v>0.09004841440736636</v>
       </c>
       <c r="T13">
-        <v>0.6038045001237355</v>
+        <v>0.609096079641062</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.46852905102598</v>
+        <v>10.51281829677382</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08390460467848239</v>
+        <v>0.08390049744992961</v>
       </c>
       <c r="C14">
-        <v>6782.10404621351</v>
+        <v>6713.651627922872</v>
       </c>
       <c r="D14">
-        <v>7352.34404621351</v>
+        <v>7353.136627922872</v>
       </c>
       <c r="E14">
-        <v>-5860.76</v>
+        <v>-5791.514999999999</v>
       </c>
       <c r="F14">
-        <v>830.9399999999999</v>
+        <v>900.1850000000001</v>
       </c>
       <c r="G14">
         <v>260.7</v>
@@ -2423,45 +2423,45 @@
         <v>452.5</v>
       </c>
       <c r="M14">
-        <v>43.042692</v>
+        <v>48.1598975</v>
       </c>
       <c r="N14">
-        <v>409.457308</v>
+        <v>404.3401025</v>
       </c>
       <c r="O14">
-        <v>102.364327</v>
+        <v>101.085025625</v>
       </c>
       <c r="P14">
-        <v>307.092981</v>
+        <v>303.255076875</v>
       </c>
       <c r="Q14">
-        <v>314.092981</v>
+        <v>310.255076875</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09004841440736636</v>
+        <v>0.09044166373555126</v>
       </c>
       <c r="T14">
-        <v>0.609096079641062</v>
+        <v>0.614509304664534</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.51281829677382</v>
+        <v>9.395784116857808</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08390049744992961</v>
+        <v>0.08374339022137681</v>
       </c>
       <c r="C15">
-        <v>6713.651627922872</v>
+        <v>6674.852798126511</v>
       </c>
       <c r="D15">
-        <v>7353.136627922872</v>
+        <v>7383.582798126511</v>
       </c>
       <c r="E15">
-        <v>-5791.514999999999</v>
+        <v>-5722.27</v>
       </c>
       <c r="F15">
-        <v>900.1850000000001</v>
+        <v>969.4300000000001</v>
       </c>
       <c r="G15">
         <v>260.7</v>
@@ -2505,28 +2505,28 @@
         <v>452.5</v>
       </c>
       <c r="M15">
-        <v>48.1598975</v>
+        <v>51.864505</v>
       </c>
       <c r="N15">
-        <v>404.3401025</v>
+        <v>400.635495</v>
       </c>
       <c r="O15">
-        <v>101.085025625</v>
+        <v>100.15887375</v>
       </c>
       <c r="P15">
-        <v>303.255076875</v>
+        <v>300.47662125</v>
       </c>
       <c r="Q15">
-        <v>310.255076875</v>
+        <v>307.47662125</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09044166373555126</v>
+        <v>0.09084405839694978</v>
       </c>
       <c r="T15">
-        <v>0.614509304664534</v>
+        <v>0.6200484186420402</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.395784116857808</v>
+        <v>8.724656679939391</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08374339022137681</v>
+        <v>0.08358628299282403</v>
       </c>
       <c r="C16">
-        <v>6674.852798126511</v>
+        <v>6636.307145570236</v>
       </c>
       <c r="D16">
-        <v>7383.582798126511</v>
+        <v>7414.282145570236</v>
       </c>
       <c r="E16">
-        <v>-5722.27</v>
+        <v>-5653.025</v>
       </c>
       <c r="F16">
-        <v>969.4300000000001</v>
+        <v>1038.675</v>
       </c>
       <c r="G16">
         <v>260.7</v>
@@ -2587,28 +2587,28 @@
         <v>452.5</v>
       </c>
       <c r="M16">
-        <v>51.864505</v>
+        <v>55.56911250000001</v>
       </c>
       <c r="N16">
-        <v>400.635495</v>
+        <v>396.9308875</v>
       </c>
       <c r="O16">
-        <v>100.15887375</v>
+        <v>99.232721875</v>
       </c>
       <c r="P16">
-        <v>300.47662125</v>
+        <v>297.698165625</v>
       </c>
       <c r="Q16">
-        <v>307.47662125</v>
+        <v>304.698165625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09084405839694978</v>
+        <v>0.09125592116802826</v>
       </c>
       <c r="T16">
-        <v>0.6200484186420402</v>
+        <v>0.6257178647131347</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.724656679939391</v>
+        <v>8.143012901276764</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08358628299282403</v>
+        <v>0.08342917576427122</v>
       </c>
       <c r="C17">
-        <v>6636.307145570236</v>
+        <v>6598.017841408387</v>
       </c>
       <c r="D17">
-        <v>7414.282145570236</v>
+        <v>7445.237841408387</v>
       </c>
       <c r="E17">
-        <v>-5653.025</v>
+        <v>-5583.78</v>
       </c>
       <c r="F17">
-        <v>1038.675</v>
+        <v>1107.92</v>
       </c>
       <c r="G17">
         <v>260.7</v>
@@ -2669,28 +2669,28 @@
         <v>452.5</v>
       </c>
       <c r="M17">
-        <v>55.5691125</v>
+        <v>59.27372</v>
       </c>
       <c r="N17">
-        <v>396.9308875</v>
+        <v>393.22628</v>
       </c>
       <c r="O17">
-        <v>99.232721875</v>
+        <v>98.30656999999999</v>
       </c>
       <c r="P17">
-        <v>297.698165625</v>
+        <v>294.91971</v>
       </c>
       <c r="Q17">
-        <v>304.698165625</v>
+        <v>301.91971</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09125592116802826</v>
+        <v>0.09167759019556099</v>
       </c>
       <c r="T17">
-        <v>0.6257178647131347</v>
+        <v>0.6315222975954458</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.143012901276766</v>
+        <v>7.634074594946967</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08342917576427122</v>
+        <v>0.08337406853571844</v>
       </c>
       <c r="C18">
-        <v>6598.017841408387</v>
+        <v>6539.692245118056</v>
       </c>
       <c r="D18">
-        <v>7445.237841408387</v>
+        <v>7456.157245118056</v>
       </c>
       <c r="E18">
-        <v>-5583.78</v>
+        <v>-5514.535</v>
       </c>
       <c r="F18">
-        <v>1107.92</v>
+        <v>1177.165</v>
       </c>
       <c r="G18">
         <v>260.7</v>
@@ -2751,45 +2751,45 @@
         <v>452.5</v>
       </c>
       <c r="M18">
-        <v>59.27372</v>
+        <v>63.92005950000001</v>
       </c>
       <c r="N18">
-        <v>393.22628</v>
+        <v>388.5799405</v>
       </c>
       <c r="O18">
-        <v>98.30656999999999</v>
+        <v>97.14498512499999</v>
       </c>
       <c r="P18">
-        <v>294.91971</v>
+        <v>291.434955375</v>
       </c>
       <c r="Q18">
-        <v>301.91971</v>
+        <v>298.434955375</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09167759019556099</v>
+        <v>0.09210941992255234</v>
       </c>
       <c r="T18">
-        <v>0.6315222975954458</v>
+        <v>0.6374665963303427</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.634074594946967</v>
+        <v>7.079154862175932</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08337406853571844</v>
+        <v>0.08322296130716565</v>
       </c>
       <c r="C19">
-        <v>6539.692245118056</v>
+        <v>6500.55387531538</v>
       </c>
       <c r="D19">
-        <v>7456.157245118056</v>
+        <v>7486.26387531538</v>
       </c>
       <c r="E19">
-        <v>-5514.535</v>
+        <v>-5445.29</v>
       </c>
       <c r="F19">
-        <v>1177.165</v>
+        <v>1246.41</v>
       </c>
       <c r="G19">
         <v>260.7</v>
@@ -2833,28 +2833,28 @@
         <v>452.5</v>
       </c>
       <c r="M19">
-        <v>63.92005950000001</v>
+        <v>67.680063</v>
       </c>
       <c r="N19">
-        <v>388.5799405</v>
+        <v>384.819937</v>
       </c>
       <c r="O19">
-        <v>97.14498512499999</v>
+        <v>96.20498425</v>
       </c>
       <c r="P19">
-        <v>291.434955375</v>
+        <v>288.61495275</v>
       </c>
       <c r="Q19">
-        <v>298.434955375</v>
+        <v>295.61495275</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09210941992255234</v>
+        <v>0.09255178208190933</v>
       </c>
       <c r="T19">
-        <v>0.6374665963303427</v>
+        <v>0.6435558779612126</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.079154862175932</v>
+        <v>6.685868480943937</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08322296130716565</v>
+        <v>0.08307185407861287</v>
       </c>
       <c r="C20">
-        <v>6500.55387531538</v>
+        <v>6461.659621592391</v>
       </c>
       <c r="D20">
-        <v>7486.26387531538</v>
+        <v>7516.614621592391</v>
       </c>
       <c r="E20">
-        <v>-5445.29</v>
+        <v>-5376.045</v>
       </c>
       <c r="F20">
-        <v>1246.41</v>
+        <v>1315.655</v>
       </c>
       <c r="G20">
         <v>260.7</v>
@@ -2915,28 +2915,28 @@
         <v>452.5</v>
       </c>
       <c r="M20">
-        <v>67.68006299999999</v>
+        <v>71.4400665</v>
       </c>
       <c r="N20">
-        <v>384.819937</v>
+        <v>381.0599335</v>
       </c>
       <c r="O20">
-        <v>96.20498425</v>
+        <v>95.264983375</v>
       </c>
       <c r="P20">
-        <v>288.61495275</v>
+        <v>285.794950125</v>
       </c>
       <c r="Q20">
-        <v>295.61495275</v>
+        <v>292.794950125</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09255178208190933</v>
+        <v>0.09300506676371958</v>
       </c>
       <c r="T20">
-        <v>0.6435558779612126</v>
+        <v>0.6497955122249437</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.685868480943938</v>
+        <v>6.333980666157415</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08307185407861287</v>
+        <v>0.08307074685006008</v>
       </c>
       <c r="C21">
-        <v>6461.659621592391</v>
+        <v>6392.637923002549</v>
       </c>
       <c r="D21">
-        <v>7516.614621592391</v>
+        <v>7516.837923002549</v>
       </c>
       <c r="E21">
-        <v>-5376.045</v>
+        <v>-5306.799999999999</v>
       </c>
       <c r="F21">
-        <v>1315.655</v>
+        <v>1384.9</v>
       </c>
       <c r="G21">
         <v>260.7</v>
@@ -2997,45 +2997,45 @@
         <v>452.5</v>
       </c>
       <c r="M21">
-        <v>71.4400665</v>
+        <v>76.58497000000001</v>
       </c>
       <c r="N21">
-        <v>381.0599335</v>
+        <v>375.91503</v>
       </c>
       <c r="O21">
-        <v>95.264983375</v>
+        <v>93.9787575</v>
       </c>
       <c r="P21">
-        <v>285.794950125</v>
+        <v>281.9362725</v>
       </c>
       <c r="Q21">
-        <v>292.794950125</v>
+        <v>288.9362725</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09300506676371958</v>
+        <v>0.0934696835625751</v>
       </c>
       <c r="T21">
-        <v>0.6497955122249437</v>
+        <v>0.6561911373452679</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.333980666157415</v>
+        <v>5.908470030085537</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08307074685006008</v>
+        <v>0.0829271396215073</v>
       </c>
       <c r="C22">
-        <v>6392.637923002549</v>
+        <v>6352.467941240084</v>
       </c>
       <c r="D22">
-        <v>7516.837923002549</v>
+        <v>7545.912941240084</v>
       </c>
       <c r="E22">
-        <v>-5306.799999999999</v>
+        <v>-5237.554999999999</v>
       </c>
       <c r="F22">
-        <v>1384.9</v>
+        <v>1454.145</v>
       </c>
       <c r="G22">
         <v>260.7</v>
@@ -3079,28 +3079,28 @@
         <v>452.5</v>
       </c>
       <c r="M22">
-        <v>76.58497000000001</v>
+        <v>80.41421850000002</v>
       </c>
       <c r="N22">
-        <v>375.91503</v>
+        <v>372.0857815</v>
       </c>
       <c r="O22">
-        <v>93.9787575</v>
+        <v>93.021445375</v>
       </c>
       <c r="P22">
-        <v>281.9362725</v>
+        <v>279.064336125</v>
       </c>
       <c r="Q22">
-        <v>288.9362725</v>
+        <v>286.064336125</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0934696835625751</v>
+        <v>0.09394606281203455</v>
       </c>
       <c r="T22">
-        <v>0.6561911373452679</v>
+        <v>0.6627486770256004</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.908470030085537</v>
+        <v>5.627114314367177</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0829271396215073</v>
+        <v>0.0827835323929545</v>
       </c>
       <c r="C23">
-        <v>6352.467941240084</v>
+        <v>6312.523756340122</v>
       </c>
       <c r="D23">
-        <v>7545.912941240084</v>
+        <v>7575.213756340123</v>
       </c>
       <c r="E23">
-        <v>-5237.555</v>
+        <v>-5168.309999999999</v>
       </c>
       <c r="F23">
-        <v>1454.145</v>
+        <v>1523.39</v>
       </c>
       <c r="G23">
         <v>260.7</v>
@@ -3161,28 +3161,28 @@
         <v>452.5</v>
       </c>
       <c r="M23">
-        <v>80.4142185</v>
+        <v>84.24346700000001</v>
       </c>
       <c r="N23">
-        <v>372.0857815</v>
+        <v>368.256533</v>
       </c>
       <c r="O23">
-        <v>93.021445375</v>
+        <v>92.06413325</v>
       </c>
       <c r="P23">
-        <v>279.064336125</v>
+        <v>276.19239975</v>
       </c>
       <c r="Q23">
-        <v>286.064336125</v>
+        <v>283.19239975</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09394606281203455</v>
+        <v>0.09443465691404422</v>
       </c>
       <c r="T23">
-        <v>0.6627486770256004</v>
+        <v>0.6694743587490182</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.627114314367178</v>
+        <v>5.371336390986852</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0827835323929545</v>
+        <v>0.08263992516440172</v>
       </c>
       <c r="C24">
-        <v>6312.523756340122</v>
+        <v>6272.808008866783</v>
       </c>
       <c r="D24">
-        <v>7575.213756340123</v>
+        <v>7604.743008866783</v>
       </c>
       <c r="E24">
-        <v>-5168.309999999999</v>
+        <v>-5099.065</v>
       </c>
       <c r="F24">
-        <v>1523.39</v>
+        <v>1592.635</v>
       </c>
       <c r="G24">
         <v>260.7</v>
@@ -3243,28 +3243,28 @@
         <v>452.5</v>
       </c>
       <c r="M24">
-        <v>84.24346700000001</v>
+        <v>88.0727155</v>
       </c>
       <c r="N24">
-        <v>368.256533</v>
+        <v>364.4272845</v>
       </c>
       <c r="O24">
-        <v>92.06413325</v>
+        <v>91.106821125</v>
       </c>
       <c r="P24">
-        <v>276.19239975</v>
+        <v>273.320463375</v>
       </c>
       <c r="Q24">
-        <v>283.19239975</v>
+        <v>280.320463375</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09443465691404422</v>
+        <v>0.09493594177195028</v>
       </c>
       <c r="T24">
-        <v>0.6694743587490182</v>
+        <v>0.6763747335042133</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.371336390986852</v>
+        <v>5.137800026161337</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08263992516440172</v>
+        <v>0.08249631793584891</v>
       </c>
       <c r="C25">
-        <v>6272.808008866783</v>
+        <v>6233.323380718501</v>
       </c>
       <c r="D25">
-        <v>7604.743008866783</v>
+        <v>7634.503380718501</v>
       </c>
       <c r="E25">
-        <v>-5099.065</v>
+        <v>-5029.82</v>
       </c>
       <c r="F25">
-        <v>1592.635</v>
+        <v>1661.88</v>
       </c>
       <c r="G25">
         <v>260.7</v>
@@ -3325,28 +3325,28 @@
         <v>452.5</v>
       </c>
       <c r="M25">
-        <v>88.0727155</v>
+        <v>91.90196400000001</v>
       </c>
       <c r="N25">
-        <v>364.4272845</v>
+        <v>360.598036</v>
       </c>
       <c r="O25">
-        <v>91.106821125</v>
+        <v>90.14950899999999</v>
       </c>
       <c r="P25">
-        <v>273.320463375</v>
+        <v>270.448527</v>
       </c>
       <c r="Q25">
-        <v>280.320463375</v>
+        <v>277.448527</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09493594177195028</v>
+        <v>0.09545041833664331</v>
       </c>
       <c r="T25">
-        <v>0.6763747335042133</v>
+        <v>0.6834566970687556</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.137800026161337</v>
+        <v>4.923725025071281</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08249631793584891</v>
+        <v>0.08235271070729612</v>
       </c>
       <c r="C26">
-        <v>6233.323380718501</v>
+        <v>6194.072595939946</v>
       </c>
       <c r="D26">
-        <v>7634.503380718501</v>
+        <v>7664.497595939946</v>
       </c>
       <c r="E26">
-        <v>-5029.82</v>
+        <v>-4960.575</v>
       </c>
       <c r="F26">
-        <v>1661.88</v>
+        <v>1731.125</v>
       </c>
       <c r="G26">
         <v>260.7</v>
@@ -3407,28 +3407,28 @@
         <v>452.5</v>
       </c>
       <c r="M26">
-        <v>91.90196399999999</v>
+        <v>95.7312125</v>
       </c>
       <c r="N26">
-        <v>360.598036</v>
+        <v>356.7687875</v>
       </c>
       <c r="O26">
-        <v>90.14950899999999</v>
+        <v>89.19219687500001</v>
       </c>
       <c r="P26">
-        <v>270.448527</v>
+        <v>267.576590625</v>
       </c>
       <c r="Q26">
-        <v>277.448527</v>
+        <v>274.576590625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09545041833664331</v>
+        <v>0.09597861427639483</v>
       </c>
       <c r="T26">
-        <v>0.6834566970687556</v>
+        <v>0.6907275129950188</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.923725025071281</v>
+        <v>4.72677602406843</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08235271070729612</v>
+        <v>0.08220910347874334</v>
       </c>
       <c r="C27">
-        <v>6194.072595939946</v>
+        <v>6155.058421553242</v>
       </c>
       <c r="D27">
-        <v>7664.497595939946</v>
+        <v>7694.728421553242</v>
       </c>
       <c r="E27">
-        <v>-4960.575</v>
+        <v>-4891.33</v>
       </c>
       <c r="F27">
-        <v>1731.125</v>
+        <v>1800.37</v>
       </c>
       <c r="G27">
         <v>260.7</v>
@@ -3489,28 +3489,28 @@
         <v>452.5</v>
       </c>
       <c r="M27">
-        <v>95.7312125</v>
+        <v>99.560461</v>
       </c>
       <c r="N27">
-        <v>356.7687875</v>
+        <v>352.939539</v>
       </c>
       <c r="O27">
-        <v>89.19219687500001</v>
+        <v>88.23488474999999</v>
       </c>
       <c r="P27">
-        <v>267.576590625</v>
+        <v>264.70465425</v>
       </c>
       <c r="Q27">
-        <v>274.576590625</v>
+        <v>271.70465425</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09597861427639483</v>
+        <v>0.0965210857820856</v>
       </c>
       <c r="T27">
-        <v>0.6907275129950188</v>
+        <v>0.6981948374598299</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.72677602406843</v>
+        <v>4.544976946219644</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08220910347874334</v>
+        <v>0.08257174625019056</v>
       </c>
       <c r="C28">
-        <v>6155.058421553242</v>
+        <v>6009.928049633727</v>
       </c>
       <c r="D28">
-        <v>7694.728421553242</v>
+        <v>7618.843049633728</v>
       </c>
       <c r="E28">
-        <v>-4891.33</v>
+        <v>-4822.084999999999</v>
       </c>
       <c r="F28">
-        <v>1800.37</v>
+        <v>1869.615</v>
       </c>
       <c r="G28">
         <v>260.7</v>
@@ -3571,45 +3571,45 @@
         <v>452.5</v>
       </c>
       <c r="M28">
-        <v>99.560461</v>
+        <v>108.063747</v>
       </c>
       <c r="N28">
-        <v>352.939539</v>
+        <v>344.436253</v>
       </c>
       <c r="O28">
-        <v>88.23488474999999</v>
+        <v>86.10906324999999</v>
       </c>
       <c r="P28">
-        <v>264.70465425</v>
+        <v>258.32718975</v>
       </c>
       <c r="Q28">
-        <v>271.70465425</v>
+        <v>265.32718975</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0965210857820856</v>
+        <v>0.09707841952080898</v>
       </c>
       <c r="T28">
-        <v>0.6981948374598299</v>
+        <v>0.7058667461565535</v>
       </c>
       <c r="U28">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.544976946219644</v>
+        <v>4.187343235470077</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08257174625019056</v>
+        <v>0.08244688902163776</v>
       </c>
       <c r="C29">
-        <v>6009.928049633727</v>
+        <v>5966.640713526955</v>
       </c>
       <c r="D29">
-        <v>7618.843049633728</v>
+        <v>7644.800713526954</v>
       </c>
       <c r="E29">
-        <v>-4822.084999999999</v>
+        <v>-4752.84</v>
       </c>
       <c r="F29">
-        <v>1869.615</v>
+        <v>1938.86</v>
       </c>
       <c r="G29">
         <v>260.7</v>
@@ -3653,28 +3653,28 @@
         <v>452.5</v>
       </c>
       <c r="M29">
-        <v>108.063747</v>
+        <v>112.066108</v>
       </c>
       <c r="N29">
-        <v>344.436253</v>
+        <v>340.433892</v>
       </c>
       <c r="O29">
-        <v>86.10906324999999</v>
+        <v>85.108473</v>
       </c>
       <c r="P29">
-        <v>258.32718975</v>
+        <v>255.325419</v>
       </c>
       <c r="Q29">
-        <v>265.32718975</v>
+        <v>262.325419</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09707841952080898</v>
+        <v>0.09765123475227466</v>
       </c>
       <c r="T29">
-        <v>0.7058667461565535</v>
+        <v>0.7137517634281861</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.187343235470077</v>
+        <v>4.037795262774718</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08244688902163776</v>
+        <v>0.08308328179308497</v>
       </c>
       <c r="C30">
-        <v>5966.640713526955</v>
+        <v>5766.905700865425</v>
       </c>
       <c r="D30">
-        <v>7644.800713526954</v>
+        <v>7514.310700865426</v>
       </c>
       <c r="E30">
-        <v>-4752.84</v>
+        <v>-4683.594999999999</v>
       </c>
       <c r="F30">
-        <v>1938.86</v>
+        <v>2008.105</v>
       </c>
       <c r="G30">
         <v>260.7</v>
@@ -3735,45 +3735,45 @@
         <v>452.5</v>
       </c>
       <c r="M30">
-        <v>112.066108</v>
+        <v>123.0968365</v>
       </c>
       <c r="N30">
-        <v>340.433892</v>
+        <v>329.4031635</v>
       </c>
       <c r="O30">
-        <v>85.108473</v>
+        <v>82.350790875</v>
       </c>
       <c r="P30">
-        <v>255.325419</v>
+        <v>247.052372625</v>
       </c>
       <c r="Q30">
-        <v>262.325419</v>
+        <v>254.052372625</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09765123475227466</v>
+        <v>0.09824018562406334</v>
       </c>
       <c r="T30">
-        <v>0.7137517634281861</v>
+        <v>0.7218588938623999</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.037795262774718</v>
+        <v>3.675967741055636</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08308328179308497</v>
+        <v>0.08298467456453217</v>
       </c>
       <c r="C31">
-        <v>5766.905700865426</v>
+        <v>5717.587333581037</v>
       </c>
       <c r="D31">
-        <v>7514.310700865426</v>
+        <v>7534.237333581038</v>
       </c>
       <c r="E31">
-        <v>-4683.595</v>
+        <v>-4614.35</v>
       </c>
       <c r="F31">
-        <v>2008.105</v>
+        <v>2077.35</v>
       </c>
       <c r="G31">
         <v>260.7</v>
@@ -3817,28 +3817,28 @@
         <v>452.5</v>
       </c>
       <c r="M31">
-        <v>123.0968365</v>
+        <v>127.341555</v>
       </c>
       <c r="N31">
-        <v>329.4031635</v>
+        <v>325.158445</v>
       </c>
       <c r="O31">
-        <v>82.350790875</v>
+        <v>81.28961125000001</v>
       </c>
       <c r="P31">
-        <v>247.052372625</v>
+        <v>243.86883375</v>
       </c>
       <c r="Q31">
-        <v>254.052372625</v>
+        <v>250.86883375</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09824018562406334</v>
+        <v>0.09884596366361739</v>
       </c>
       <c r="T31">
-        <v>0.7218588938623999</v>
+        <v>0.7301976565947341</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.675967741055636</v>
+        <v>3.553435483020449</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08298467456453217</v>
+        <v>0.08353706733597939</v>
       </c>
       <c r="C32">
-        <v>5717.587333581037</v>
+        <v>5538.056650690412</v>
       </c>
       <c r="D32">
-        <v>7534.237333581038</v>
+        <v>7423.951650690412</v>
       </c>
       <c r="E32">
-        <v>-4614.35</v>
+        <v>-4545.105</v>
       </c>
       <c r="F32">
-        <v>2077.35</v>
+        <v>2146.595</v>
       </c>
       <c r="G32">
         <v>260.7</v>
@@ -3899,45 +3899,45 @@
         <v>452.5</v>
       </c>
       <c r="M32">
-        <v>127.341555</v>
+        <v>137.5967395</v>
       </c>
       <c r="N32">
-        <v>325.158445</v>
+        <v>314.9032605</v>
       </c>
       <c r="O32">
-        <v>81.28961125000001</v>
+        <v>78.725815125</v>
       </c>
       <c r="P32">
-        <v>243.86883375</v>
+        <v>236.177445375</v>
       </c>
       <c r="Q32">
-        <v>250.86883375</v>
+        <v>243.177445375</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09884596366361739</v>
+        <v>0.09946930048692665</v>
       </c>
       <c r="T32">
-        <v>0.7301976565947341</v>
+        <v>0.7387781225946722</v>
       </c>
       <c r="U32">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.553435483020449</v>
+        <v>3.288595366752858</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08353706733597939</v>
+        <v>0.08345946010742658</v>
       </c>
       <c r="C33">
-        <v>5538.056650690412</v>
+        <v>5484.110656859821</v>
       </c>
       <c r="D33">
-        <v>7423.951650690412</v>
+        <v>7439.250656859821</v>
       </c>
       <c r="E33">
-        <v>-4545.105</v>
+        <v>-4475.86</v>
       </c>
       <c r="F33">
-        <v>2146.595</v>
+        <v>2215.84</v>
       </c>
       <c r="G33">
         <v>260.7</v>
@@ -3981,28 +3981,28 @@
         <v>452.5</v>
       </c>
       <c r="M33">
-        <v>137.5967395</v>
+        <v>142.035344</v>
       </c>
       <c r="N33">
-        <v>314.9032605</v>
+        <v>310.464656</v>
       </c>
       <c r="O33">
-        <v>78.725815125</v>
+        <v>77.616164</v>
       </c>
       <c r="P33">
-        <v>236.177445375</v>
+        <v>232.848492</v>
       </c>
       <c r="Q33">
-        <v>243.177445375</v>
+        <v>239.848492</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09946930048692665</v>
+        <v>0.1001109707462156</v>
       </c>
       <c r="T33">
-        <v>0.7387781225946722</v>
+        <v>0.7476109552416675</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.288595366752858</v>
+        <v>3.185826761541831</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08345946010742658</v>
+        <v>0.08338185287887381</v>
       </c>
       <c r="C34">
-        <v>5484.110656859821</v>
+        <v>5430.227848496541</v>
       </c>
       <c r="D34">
-        <v>7439.250656859821</v>
+        <v>7454.612848496541</v>
       </c>
       <c r="E34">
-        <v>-4475.86</v>
+        <v>-4406.615</v>
       </c>
       <c r="F34">
-        <v>2215.84</v>
+        <v>2285.085</v>
       </c>
       <c r="G34">
         <v>260.7</v>
@@ -4063,28 +4063,28 @@
         <v>452.5</v>
       </c>
       <c r="M34">
-        <v>142.035344</v>
+        <v>146.4739485</v>
       </c>
       <c r="N34">
-        <v>310.464656</v>
+        <v>306.0260515</v>
       </c>
       <c r="O34">
-        <v>77.616164</v>
+        <v>76.506512875</v>
       </c>
       <c r="P34">
-        <v>232.848492</v>
+        <v>229.519538625</v>
       </c>
       <c r="Q34">
-        <v>239.848492</v>
+        <v>236.519538625</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1001109707462156</v>
+        <v>0.1007717953416027</v>
       </c>
       <c r="T34">
-        <v>0.7476109552416675</v>
+        <v>0.7567074545348416</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.185826761541831</v>
+        <v>3.089286556646624</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08338185287887381</v>
+        <v>0.08529324565032102</v>
       </c>
       <c r="C35">
-        <v>5430.227848496541</v>
+        <v>5000.194747191475</v>
       </c>
       <c r="D35">
-        <v>7454.612848496541</v>
+        <v>7093.824747191476</v>
       </c>
       <c r="E35">
-        <v>-4406.615</v>
+        <v>-4337.369999999999</v>
       </c>
       <c r="F35">
-        <v>2285.085</v>
+        <v>2354.33</v>
       </c>
       <c r="G35">
         <v>260.7</v>
@@ -4145,45 +4145,45 @@
         <v>452.5</v>
       </c>
       <c r="M35">
-        <v>146.4739485</v>
+        <v>169.276327</v>
       </c>
       <c r="N35">
-        <v>306.0260515</v>
+        <v>283.223673</v>
       </c>
       <c r="O35">
-        <v>76.506512875</v>
+        <v>70.80591824999999</v>
       </c>
       <c r="P35">
-        <v>229.519538625</v>
+        <v>212.41775475</v>
       </c>
       <c r="Q35">
-        <v>236.519538625</v>
+        <v>219.41775475</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1007717953416027</v>
+        <v>0.1014526449247288</v>
       </c>
       <c r="T35">
-        <v>0.7567074545348416</v>
+        <v>0.7660796053217482</v>
       </c>
       <c r="U35">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.089286556646624</v>
+        <v>2.673144012629716</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08529324565032102</v>
+        <v>0.08527413842176823</v>
       </c>
       <c r="C36">
-        <v>5000.194747191475</v>
+        <v>4934.383472059892</v>
       </c>
       <c r="D36">
-        <v>7093.824747191476</v>
+        <v>7097.258472059892</v>
       </c>
       <c r="E36">
-        <v>-4337.369999999999</v>
+        <v>-4268.125</v>
       </c>
       <c r="F36">
-        <v>2354.33</v>
+        <v>2423.575</v>
       </c>
       <c r="G36">
         <v>260.7</v>
@@ -4227,28 +4227,28 @@
         <v>452.5</v>
       </c>
       <c r="M36">
-        <v>169.276327</v>
+        <v>174.2550425</v>
       </c>
       <c r="N36">
-        <v>283.223673</v>
+        <v>278.2449574999999</v>
       </c>
       <c r="O36">
-        <v>70.80591824999999</v>
+        <v>69.56123937499999</v>
       </c>
       <c r="P36">
-        <v>212.41775475</v>
+        <v>208.683718125</v>
       </c>
       <c r="Q36">
-        <v>219.41775475</v>
+        <v>215.683718125</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1014526449247288</v>
+        <v>0.1021544437257973</v>
       </c>
       <c r="T36">
-        <v>0.7660796053217482</v>
+        <v>0.7757401299790212</v>
       </c>
       <c r="U36">
         <v>0.07190000000000001</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.673144012629716</v>
+        <v>2.596768469411724</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08527413842176823</v>
+        <v>0.08525503119321542</v>
       </c>
       <c r="C37">
-        <v>4934.383472059892</v>
+        <v>4868.575522687475</v>
       </c>
       <c r="D37">
-        <v>7097.258472059892</v>
+        <v>7100.695522687475</v>
       </c>
       <c r="E37">
-        <v>-4268.125</v>
+        <v>-4198.879999999999</v>
       </c>
       <c r="F37">
-        <v>2423.575</v>
+        <v>2492.82</v>
       </c>
       <c r="G37">
         <v>260.7</v>
@@ -4309,28 +4309,28 @@
         <v>452.5</v>
       </c>
       <c r="M37">
-        <v>174.2550425</v>
+        <v>179.233758</v>
       </c>
       <c r="N37">
-        <v>278.2449574999999</v>
+        <v>273.266242</v>
       </c>
       <c r="O37">
-        <v>69.56123937499999</v>
+        <v>68.31656049999999</v>
       </c>
       <c r="P37">
-        <v>208.683718125</v>
+        <v>204.9496815</v>
       </c>
       <c r="Q37">
-        <v>215.683718125</v>
+        <v>211.9496815</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1021544437257973</v>
+        <v>0.1028781737393991</v>
       </c>
       <c r="T37">
-        <v>0.7757401299790212</v>
+        <v>0.7857025460318339</v>
       </c>
       <c r="U37">
         <v>0.07190000000000001</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.596768469411724</v>
+        <v>2.524636011928065</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08525503119321544</v>
+        <v>0.08631817396466265</v>
       </c>
       <c r="C38">
-        <v>4868.575522687473</v>
+        <v>4613.017755390098</v>
       </c>
       <c r="D38">
-        <v>7100.695522687472</v>
+        <v>6914.382755390097</v>
       </c>
       <c r="E38">
-        <v>-4198.88</v>
+        <v>-4129.635</v>
       </c>
       <c r="F38">
-        <v>2492.82</v>
+        <v>2562.065</v>
       </c>
       <c r="G38">
         <v>260.7</v>
@@ -4391,45 +4391,45 @@
         <v>452.5</v>
       </c>
       <c r="M38">
-        <v>179.233758</v>
+        <v>194.204527</v>
       </c>
       <c r="N38">
-        <v>273.266242</v>
+        <v>258.295473</v>
       </c>
       <c r="O38">
-        <v>68.31656050000001</v>
+        <v>64.57386825</v>
       </c>
       <c r="P38">
-        <v>204.9496815</v>
+        <v>193.72160475</v>
       </c>
       <c r="Q38">
-        <v>211.9496815</v>
+        <v>200.72160475</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1028781737393991</v>
+        <v>0.1036248793089883</v>
       </c>
       <c r="T38">
-        <v>0.7857025460318339</v>
+        <v>0.7959812292609264</v>
       </c>
       <c r="U38">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.524636011928066</v>
+        <v>2.33001777553826</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08631817396466265</v>
+        <v>0.08632831673610986</v>
       </c>
       <c r="C39">
-        <v>4613.017755390098</v>
+        <v>4542.04233553469</v>
       </c>
       <c r="D39">
-        <v>6914.382755390097</v>
+        <v>6912.65233553469</v>
       </c>
       <c r="E39">
-        <v>-4129.635</v>
+        <v>-4060.39</v>
       </c>
       <c r="F39">
-        <v>2562.065</v>
+        <v>2631.31</v>
       </c>
       <c r="G39">
         <v>260.7</v>
@@ -4473,28 +4473,28 @@
         <v>452.5</v>
       </c>
       <c r="M39">
-        <v>194.204527</v>
+        <v>199.453298</v>
       </c>
       <c r="N39">
-        <v>258.295473</v>
+        <v>253.046702</v>
       </c>
       <c r="O39">
-        <v>64.57386825</v>
+        <v>63.2616755</v>
       </c>
       <c r="P39">
-        <v>193.72160475</v>
+        <v>189.7850265</v>
       </c>
       <c r="Q39">
-        <v>200.72160475</v>
+        <v>196.7850265</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1036248793089883</v>
+        <v>0.1043956721550159</v>
       </c>
       <c r="T39">
-        <v>0.7959812292609264</v>
+        <v>0.806591482916764</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.33001777553826</v>
+        <v>2.268701518287253</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08632831673610986</v>
+        <v>0.08633845950755709</v>
       </c>
       <c r="C40">
-        <v>4542.04233553469</v>
+        <v>4471.067781585545</v>
       </c>
       <c r="D40">
-        <v>6912.65233553469</v>
+        <v>6910.922781585546</v>
       </c>
       <c r="E40">
-        <v>-4060.39</v>
+        <v>-3991.145</v>
       </c>
       <c r="F40">
-        <v>2631.31</v>
+        <v>2700.555</v>
       </c>
       <c r="G40">
         <v>260.7</v>
@@ -4555,28 +4555,28 @@
         <v>452.5</v>
       </c>
       <c r="M40">
-        <v>199.453298</v>
+        <v>204.7020690000001</v>
       </c>
       <c r="N40">
-        <v>253.046702</v>
+        <v>247.7979309999999</v>
       </c>
       <c r="O40">
-        <v>63.2616755</v>
+        <v>61.94948274999999</v>
       </c>
       <c r="P40">
-        <v>189.7850265</v>
+        <v>185.84844825</v>
       </c>
       <c r="Q40">
-        <v>196.7850265</v>
+        <v>192.84844825</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1043956721550159</v>
+        <v>0.1051917368976345</v>
       </c>
       <c r="T40">
-        <v>0.806591482916764</v>
+        <v>0.8175496137416453</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.268701518287253</v>
+        <v>2.210529684485016</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08633845950755709</v>
+        <v>0.08634860227900429</v>
       </c>
       <c r="C41">
-        <v>4471.067781585545</v>
+        <v>4400.094092892886</v>
       </c>
       <c r="D41">
-        <v>6910.922781585546</v>
+        <v>6909.194092892886</v>
       </c>
       <c r="E41">
-        <v>-3991.145</v>
+        <v>-3921.9</v>
       </c>
       <c r="F41">
-        <v>2700.555</v>
+        <v>2769.8</v>
       </c>
       <c r="G41">
         <v>260.7</v>
@@ -4637,28 +4637,28 @@
         <v>452.5</v>
       </c>
       <c r="M41">
-        <v>204.7020690000001</v>
+        <v>209.95084</v>
       </c>
       <c r="N41">
-        <v>247.7979309999999</v>
+        <v>242.54916</v>
       </c>
       <c r="O41">
-        <v>61.94948274999999</v>
+        <v>60.63728999999999</v>
       </c>
       <c r="P41">
-        <v>185.84844825</v>
+        <v>181.91187</v>
       </c>
       <c r="Q41">
-        <v>192.84844825</v>
+        <v>188.91187</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1051917368976345</v>
+        <v>0.1060143371316738</v>
       </c>
       <c r="T41">
-        <v>0.8175496137416453</v>
+        <v>0.8288730155940226</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.210529684485016</v>
+        <v>2.15526644237289</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08634860227900429</v>
+        <v>0.08635874505045149</v>
       </c>
       <c r="C42">
-        <v>4400.094092892886</v>
+        <v>4329.121268807565</v>
       </c>
       <c r="D42">
-        <v>6909.194092892886</v>
+        <v>6907.466268807565</v>
       </c>
       <c r="E42">
-        <v>-3921.9</v>
+        <v>-3852.655</v>
       </c>
       <c r="F42">
-        <v>2769.8</v>
+        <v>2839.045</v>
       </c>
       <c r="G42">
         <v>260.7</v>
@@ -4719,28 +4719,28 @@
         <v>452.5</v>
       </c>
       <c r="M42">
-        <v>209.95084</v>
+        <v>215.199611</v>
       </c>
       <c r="N42">
-        <v>242.54916</v>
+        <v>237.300389</v>
       </c>
       <c r="O42">
-        <v>60.63728999999999</v>
+        <v>59.32509724999999</v>
       </c>
       <c r="P42">
-        <v>181.91187</v>
+        <v>177.97529175</v>
       </c>
       <c r="Q42">
-        <v>188.91187</v>
+        <v>184.97529175</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1060143371316738</v>
+        <v>0.1068648221194093</v>
       </c>
       <c r="T42">
-        <v>0.8288730155940226</v>
+        <v>0.8405802615769891</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.15526644237289</v>
+        <v>2.102698968168673</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08635874505045149</v>
+        <v>0.08636888782189871</v>
       </c>
       <c r="C43">
-        <v>4329.121268807565</v>
+        <v>4258.149308681088</v>
       </c>
       <c r="D43">
-        <v>6907.466268807565</v>
+        <v>6905.739308681089</v>
       </c>
       <c r="E43">
-        <v>-3852.655</v>
+        <v>-3783.409999999999</v>
       </c>
       <c r="F43">
-        <v>2839.045</v>
+        <v>2908.29</v>
       </c>
       <c r="G43">
         <v>260.7</v>
@@ -4801,28 +4801,28 @@
         <v>452.5</v>
       </c>
       <c r="M43">
-        <v>215.199611</v>
+        <v>220.448382</v>
       </c>
       <c r="N43">
-        <v>237.300389</v>
+        <v>232.051618</v>
       </c>
       <c r="O43">
-        <v>59.32509724999999</v>
+        <v>58.01290449999999</v>
       </c>
       <c r="P43">
-        <v>177.97529175</v>
+        <v>174.0387135</v>
       </c>
       <c r="Q43">
-        <v>184.97529175</v>
+        <v>181.0387135</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1068648221194093</v>
+        <v>0.1077446341756874</v>
       </c>
       <c r="T43">
-        <v>0.8405802615769891</v>
+        <v>0.8526912056972992</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.102698968168673</v>
+        <v>2.052634707021801</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08636888782189872</v>
+        <v>0.08637903059334592</v>
       </c>
       <c r="C44">
-        <v>4258.149308681088</v>
+        <v>4187.178211865619</v>
       </c>
       <c r="D44">
-        <v>6905.739308681088</v>
+        <v>6904.013211865619</v>
       </c>
       <c r="E44">
-        <v>-3783.41</v>
+        <v>-3714.165</v>
       </c>
       <c r="F44">
-        <v>2908.29</v>
+        <v>2977.535</v>
       </c>
       <c r="G44">
         <v>260.7</v>
@@ -4883,28 +4883,28 @@
         <v>452.5</v>
       </c>
       <c r="M44">
-        <v>220.448382</v>
+        <v>225.697153</v>
       </c>
       <c r="N44">
-        <v>232.051618</v>
+        <v>226.802847</v>
       </c>
       <c r="O44">
-        <v>58.0129045</v>
+        <v>56.70071175</v>
       </c>
       <c r="P44">
-        <v>174.0387135</v>
+        <v>170.10213525</v>
       </c>
       <c r="Q44">
-        <v>181.0387135</v>
+        <v>177.10213525</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1077446341756874</v>
+        <v>0.1086553168304314</v>
       </c>
       <c r="T44">
-        <v>0.8526912056972992</v>
+        <v>0.8652270952253394</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.052634707021801</v>
+        <v>2.004899016160828</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08637903059334592</v>
+        <v>0.09107517336479314</v>
       </c>
       <c r="C45">
-        <v>4187.178211865619</v>
+        <v>3401.818190557033</v>
       </c>
       <c r="D45">
-        <v>6904.013211865619</v>
+        <v>6187.898190557034</v>
       </c>
       <c r="E45">
-        <v>-3714.165</v>
+        <v>-3644.92</v>
       </c>
       <c r="F45">
-        <v>2977.535</v>
+        <v>3046.78</v>
       </c>
       <c r="G45">
         <v>260.7</v>
@@ -4965,45 +4965,45 @@
         <v>452.5</v>
       </c>
       <c r="M45">
-        <v>225.697153</v>
+        <v>274.2102</v>
       </c>
       <c r="N45">
-        <v>226.802847</v>
+        <v>178.2898</v>
       </c>
       <c r="O45">
-        <v>56.70071175</v>
+        <v>44.57245</v>
       </c>
       <c r="P45">
-        <v>170.10213525</v>
+        <v>133.71735</v>
       </c>
       <c r="Q45">
-        <v>177.10213525</v>
+        <v>140.71735</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1086553168304314</v>
+        <v>0.109598523865702</v>
       </c>
       <c r="T45">
-        <v>0.8652270952253394</v>
+        <v>0.8782106950936669</v>
       </c>
       <c r="U45">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.004899016160828</v>
+        <v>1.650193902342072</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09107517336479314</v>
+        <v>0.09119181613624035</v>
       </c>
       <c r="C46">
-        <v>3401.818190557033</v>
+        <v>3316.672227435985</v>
       </c>
       <c r="D46">
-        <v>6187.898190557034</v>
+        <v>6171.997227435985</v>
       </c>
       <c r="E46">
-        <v>-3644.92</v>
+        <v>-3575.675</v>
       </c>
       <c r="F46">
-        <v>3046.78</v>
+        <v>3116.025</v>
       </c>
       <c r="G46">
         <v>260.7</v>
@@ -5047,28 +5047,28 @@
         <v>452.5</v>
       </c>
       <c r="M46">
-        <v>274.2102</v>
+        <v>280.44225</v>
       </c>
       <c r="N46">
-        <v>178.2898</v>
+        <v>172.05775</v>
       </c>
       <c r="O46">
-        <v>44.57245</v>
+        <v>43.0144375</v>
       </c>
       <c r="P46">
-        <v>133.71735</v>
+        <v>129.0433125</v>
       </c>
       <c r="Q46">
-        <v>140.71735</v>
+        <v>136.0433125</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.109598523865702</v>
+        <v>0.1105760293386188</v>
       </c>
       <c r="T46">
-        <v>0.8782106950936669</v>
+        <v>0.891666425866297</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.650193902342072</v>
+        <v>1.61352292673447</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09119181613624035</v>
+        <v>0.09130845890768756</v>
       </c>
       <c r="C47">
-        <v>3316.672227435985</v>
+        <v>3231.607775860335</v>
       </c>
       <c r="D47">
-        <v>6171.997227435985</v>
+        <v>6156.177775860335</v>
       </c>
       <c r="E47">
-        <v>-3575.675</v>
+        <v>-3506.43</v>
       </c>
       <c r="F47">
-        <v>3116.025</v>
+        <v>3185.27</v>
       </c>
       <c r="G47">
         <v>260.7</v>
@@ -5129,28 +5129,28 @@
         <v>452.5</v>
       </c>
       <c r="M47">
-        <v>280.44225</v>
+        <v>286.6743</v>
       </c>
       <c r="N47">
-        <v>172.05775</v>
+        <v>165.8257</v>
       </c>
       <c r="O47">
-        <v>43.0144375</v>
+        <v>41.45642500000001</v>
       </c>
       <c r="P47">
-        <v>129.0433125</v>
+        <v>124.369275</v>
       </c>
       <c r="Q47">
-        <v>136.0433125</v>
+        <v>131.369275</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1105760293386188</v>
+        <v>0.1115897387179399</v>
       </c>
       <c r="T47">
-        <v>0.891666425866297</v>
+        <v>0.9056205170379136</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.61352292673447</v>
+        <v>1.578446341370678</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09130845890768756</v>
+        <v>0.09142510167913476</v>
       </c>
       <c r="C48">
-        <v>3231.607775860335</v>
+        <v>3146.6242106655</v>
       </c>
       <c r="D48">
-        <v>6156.177775860335</v>
+        <v>6140.4392106655</v>
       </c>
       <c r="E48">
-        <v>-3506.43</v>
+        <v>-3437.184999999999</v>
       </c>
       <c r="F48">
-        <v>3185.27</v>
+        <v>3254.515</v>
       </c>
       <c r="G48">
         <v>260.7</v>
@@ -5211,28 +5211,28 @@
         <v>452.5</v>
       </c>
       <c r="M48">
-        <v>286.6743</v>
+        <v>292.90635</v>
       </c>
       <c r="N48">
-        <v>165.8257</v>
+        <v>159.59365</v>
       </c>
       <c r="O48">
-        <v>41.45642500000001</v>
+        <v>39.89841249999999</v>
       </c>
       <c r="P48">
-        <v>124.369275</v>
+        <v>119.6952375</v>
       </c>
       <c r="Q48">
-        <v>131.369275</v>
+        <v>126.6952375</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1115897387179399</v>
+        <v>0.1126417012813863</v>
       </c>
       <c r="T48">
-        <v>0.9056205170379136</v>
+        <v>0.9201011776877043</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.578446341370678</v>
+        <v>1.544862376660663</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09142510167913476</v>
+        <v>0.09154174445058197</v>
       </c>
       <c r="C49">
-        <v>3146.6242106655</v>
+        <v>3061.720913063647</v>
       </c>
       <c r="D49">
-        <v>6140.4392106655</v>
+        <v>6124.780913063647</v>
       </c>
       <c r="E49">
-        <v>-3437.184999999999</v>
+        <v>-3367.94</v>
       </c>
       <c r="F49">
-        <v>3254.515</v>
+        <v>3323.76</v>
       </c>
       <c r="G49">
         <v>260.7</v>
@@ -5293,28 +5293,28 @@
         <v>452.5</v>
       </c>
       <c r="M49">
-        <v>292.90635</v>
+        <v>299.1384</v>
       </c>
       <c r="N49">
-        <v>159.59365</v>
+        <v>153.3616</v>
       </c>
       <c r="O49">
-        <v>39.89841249999999</v>
+        <v>38.3404</v>
       </c>
       <c r="P49">
-        <v>119.6952375</v>
+        <v>115.0212</v>
       </c>
       <c r="Q49">
-        <v>126.6952375</v>
+        <v>122.0212</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1126417012813863</v>
+        <v>0.1137341239434269</v>
       </c>
       <c r="T49">
-        <v>0.9201011776877043</v>
+        <v>0.9351387868240255</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.544862376660663</v>
+        <v>1.512677743813566</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09154174445058197</v>
+        <v>0.114628593102708</v>
       </c>
       <c r="C50">
-        <v>3061.720913063647</v>
+        <v>938.0696904008273</v>
       </c>
       <c r="D50">
-        <v>6124.780913063647</v>
+        <v>4070.374690400828</v>
       </c>
       <c r="E50">
-        <v>-3367.94</v>
+        <v>-3298.695</v>
       </c>
       <c r="F50">
-        <v>3323.76</v>
+        <v>3393.005</v>
       </c>
       <c r="G50">
         <v>260.7</v>
@@ -5375,45 +5375,45 @@
         <v>452.5</v>
       </c>
       <c r="M50">
-        <v>299.1384</v>
+        <v>498.0931340000001</v>
       </c>
       <c r="N50">
-        <v>153.3616</v>
+        <v>-45.59313400000008</v>
       </c>
       <c r="O50">
-        <v>38.3404</v>
+        <v>-11.39828350000002</v>
       </c>
       <c r="P50">
-        <v>115.0212</v>
+        <v>-34.19485050000006</v>
       </c>
       <c r="Q50">
-        <v>122.0212</v>
+        <v>-27.19485050000006</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1137341239434269</v>
+        <v>0.1157519857566558</v>
       </c>
       <c r="T50">
-        <v>0.9351387868240255</v>
+        <v>0.9629154142163632</v>
       </c>
       <c r="U50">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.25</v>
+        <v>0.2271161601677488</v>
       </c>
       <c r="W50">
-        <v>0.0675</v>
+        <v>0.1134593476873745</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.512677743813566</v>
+        <v>0.9084646406709953</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.114628593102708</v>
+        <v>0.115638593102708</v>
       </c>
       <c r="C51">
-        <v>938.0696904008273</v>
+        <v>809.9592657886951</v>
       </c>
       <c r="D51">
-        <v>4070.374690400828</v>
+        <v>4011.509265788695</v>
       </c>
       <c r="E51">
-        <v>-3298.695</v>
+        <v>-3229.45</v>
       </c>
       <c r="F51">
-        <v>3393.005</v>
+        <v>3462.25</v>
       </c>
       <c r="G51">
         <v>260.7</v>
@@ -5457,37 +5457,37 @@
         <v>452.5</v>
       </c>
       <c r="M51">
-        <v>498.0931340000001</v>
+        <v>508.2583</v>
       </c>
       <c r="N51">
-        <v>-45.59313400000008</v>
+        <v>-55.75830000000002</v>
       </c>
       <c r="O51">
-        <v>-11.39828350000002</v>
+        <v>-13.939575</v>
       </c>
       <c r="P51">
-        <v>-34.19485050000006</v>
+        <v>-41.81872500000001</v>
       </c>
       <c r="Q51">
-        <v>-27.19485050000006</v>
+        <v>-34.81872500000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1157519857566558</v>
+        <v>0.1171510254717889</v>
       </c>
       <c r="T51">
-        <v>0.9629154142163632</v>
+        <v>0.9821737225006905</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2271161601677488</v>
+        <v>0.2225738369643939</v>
       </c>
       <c r="W51">
-        <v>0.1134593476873745</v>
+        <v>0.114126160733627</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.9084646406709953</v>
+        <v>0.8902953478575756</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.115638593102708</v>
+        <v>0.116648593102708</v>
       </c>
       <c r="C52">
-        <v>809.9592657886951</v>
+        <v>683.5271830110178</v>
       </c>
       <c r="D52">
-        <v>4011.509265788695</v>
+        <v>3954.322183011018</v>
       </c>
       <c r="E52">
-        <v>-3229.45</v>
+        <v>-3160.205</v>
       </c>
       <c r="F52">
-        <v>3462.25</v>
+        <v>3531.495</v>
       </c>
       <c r="G52">
         <v>260.7</v>
@@ -5539,37 +5539,37 @@
         <v>452.5</v>
       </c>
       <c r="M52">
-        <v>508.2583</v>
+        <v>518.4234660000001</v>
       </c>
       <c r="N52">
-        <v>-55.75830000000002</v>
+        <v>-65.92346600000008</v>
       </c>
       <c r="O52">
-        <v>-13.939575</v>
+        <v>-16.48086650000002</v>
       </c>
       <c r="P52">
-        <v>-41.81872500000001</v>
+        <v>-49.44259950000006</v>
       </c>
       <c r="Q52">
-        <v>-34.81872500000001</v>
+        <v>-42.44259950000006</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1171510254717889</v>
+        <v>0.1186071688487642</v>
       </c>
       <c r="T52">
-        <v>0.9821737225006905</v>
+        <v>1.002218084184378</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2225738369643939</v>
+        <v>0.2182096440827391</v>
       </c>
       <c r="W52">
-        <v>0.114126160733627</v>
+        <v>0.1147668242486539</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8902953478575756</v>
+        <v>0.8728385763309563</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.116648593102708</v>
+        <v>0.117658593102708</v>
       </c>
       <c r="C53">
-        <v>683.5271830110178</v>
+        <v>558.7026728592841</v>
       </c>
       <c r="D53">
-        <v>3954.322183011018</v>
+        <v>3898.742672859285</v>
       </c>
       <c r="E53">
-        <v>-3160.205</v>
+        <v>-3090.96</v>
       </c>
       <c r="F53">
-        <v>3531.495</v>
+        <v>3600.74</v>
       </c>
       <c r="G53">
         <v>260.7</v>
@@ -5621,37 +5621,37 @@
         <v>452.5</v>
       </c>
       <c r="M53">
-        <v>518.4234660000001</v>
+        <v>528.5886320000001</v>
       </c>
       <c r="N53">
-        <v>-65.92346600000008</v>
+        <v>-76.08863200000008</v>
       </c>
       <c r="O53">
-        <v>-16.48086650000002</v>
+        <v>-19.02215800000002</v>
       </c>
       <c r="P53">
-        <v>-49.44259950000006</v>
+        <v>-57.06647400000006</v>
       </c>
       <c r="Q53">
-        <v>-42.44259950000006</v>
+        <v>-50.06647400000006</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1186071688487642</v>
+        <v>0.1201239848664468</v>
       </c>
       <c r="T53">
-        <v>1.002218084184378</v>
+        <v>1.023097627604886</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.2182096440827391</v>
+        <v>0.2140133047734556</v>
       </c>
       <c r="W53">
-        <v>0.1147668242486539</v>
+        <v>0.1153828468592567</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8728385763309563</v>
+        <v>0.8560532190938226</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.117658593102708</v>
+        <v>0.118668593102708</v>
       </c>
       <c r="C54">
-        <v>558.7026728592841</v>
+        <v>435.4188897303497</v>
       </c>
       <c r="D54">
-        <v>3898.742672859285</v>
+        <v>3844.70388973035</v>
       </c>
       <c r="E54">
-        <v>-3090.96</v>
+        <v>-3021.715</v>
       </c>
       <c r="F54">
-        <v>3600.74</v>
+        <v>3669.985</v>
       </c>
       <c r="G54">
         <v>260.7</v>
@@ -5703,37 +5703,37 @@
         <v>452.5</v>
       </c>
       <c r="M54">
-        <v>528.5886320000001</v>
+        <v>538.7537980000001</v>
       </c>
       <c r="N54">
-        <v>-76.08863200000008</v>
+        <v>-86.25379800000007</v>
       </c>
       <c r="O54">
-        <v>-19.02215800000002</v>
+        <v>-21.56344950000002</v>
       </c>
       <c r="P54">
-        <v>-57.06647400000006</v>
+        <v>-64.69034850000006</v>
       </c>
       <c r="Q54">
-        <v>-50.06647400000006</v>
+        <v>-57.69034850000006</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1201239848664468</v>
+        <v>0.121705346246584</v>
       </c>
       <c r="T54">
-        <v>1.023097627604886</v>
+        <v>1.044865662234777</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2140133047734556</v>
+        <v>0.2099753178909376</v>
       </c>
       <c r="W54">
-        <v>0.1153828468592567</v>
+        <v>0.1159756233336104</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8560532190938226</v>
+        <v>0.8399012715637504</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.118668593102708</v>
+        <v>0.119678593102708</v>
       </c>
       <c r="C55">
-        <v>435.4188897303497</v>
+        <v>313.6126434268472</v>
       </c>
       <c r="D55">
-        <v>3844.70388973035</v>
+        <v>3792.142643426848</v>
       </c>
       <c r="E55">
-        <v>-3021.715</v>
+        <v>-2952.469999999999</v>
       </c>
       <c r="F55">
-        <v>3669.985</v>
+        <v>3739.23</v>
       </c>
       <c r="G55">
         <v>260.7</v>
@@ -5785,37 +5785,37 @@
         <v>452.5</v>
       </c>
       <c r="M55">
-        <v>538.7537980000001</v>
+        <v>548.9189640000001</v>
       </c>
       <c r="N55">
-        <v>-86.25379800000007</v>
+        <v>-96.41896400000007</v>
       </c>
       <c r="O55">
-        <v>-21.56344950000002</v>
+        <v>-24.10474100000002</v>
       </c>
       <c r="P55">
-        <v>-64.69034850000006</v>
+        <v>-72.31422300000006</v>
       </c>
       <c r="Q55">
-        <v>-57.69034850000006</v>
+        <v>-65.31422300000006</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.121705346246584</v>
+        <v>0.1233554624693358</v>
       </c>
       <c r="T55">
-        <v>1.044865662234777</v>
+        <v>1.067580133152925</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.2099753178909376</v>
+        <v>0.2060868860781425</v>
       </c>
       <c r="W55">
-        <v>0.1159756233336104</v>
+        <v>0.1165464451237287</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8399012715637504</v>
+        <v>0.8243475443125698</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.119678593102708</v>
+        <v>0.120688593102708</v>
       </c>
       <c r="C56">
-        <v>313.6126434268472</v>
+        <v>193.2241526603916</v>
       </c>
       <c r="D56">
-        <v>3792.142643426848</v>
+        <v>3740.999152660392</v>
       </c>
       <c r="E56">
-        <v>-2952.469999999999</v>
+        <v>-2883.224999999999</v>
       </c>
       <c r="F56">
-        <v>3739.23</v>
+        <v>3808.475</v>
       </c>
       <c r="G56">
         <v>260.7</v>
@@ -5867,37 +5867,37 @@
         <v>452.5</v>
       </c>
       <c r="M56">
-        <v>548.9189640000001</v>
+        <v>559.0841300000001</v>
       </c>
       <c r="N56">
-        <v>-96.41896400000007</v>
+        <v>-106.5841300000001</v>
       </c>
       <c r="O56">
-        <v>-24.10474100000002</v>
+        <v>-26.64603250000002</v>
       </c>
       <c r="P56">
-        <v>-72.31422300000006</v>
+        <v>-79.93809750000005</v>
       </c>
       <c r="Q56">
-        <v>-65.31422300000006</v>
+        <v>-72.93809750000005</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1233554624693358</v>
+        <v>0.1250789171908766</v>
       </c>
       <c r="T56">
-        <v>1.067580133152925</v>
+        <v>1.091304136111878</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2060868860781425</v>
+        <v>0.2023398517858126</v>
       </c>
       <c r="W56">
-        <v>0.1165464451237287</v>
+        <v>0.1170965097578427</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8243475443125698</v>
+        <v>0.8093594071432504</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.120688593102708</v>
+        <v>0.1531399798009249</v>
       </c>
       <c r="C57">
-        <v>193.2241526603916</v>
+        <v>-1007.012397420356</v>
       </c>
       <c r="D57">
-        <v>3740.999152660392</v>
+        <v>2610.007602579644</v>
       </c>
       <c r="E57">
-        <v>-2883.224999999999</v>
+        <v>-2813.98</v>
       </c>
       <c r="F57">
-        <v>3808.475</v>
+        <v>3877.72</v>
       </c>
       <c r="G57">
         <v>260.7</v>
@@ -5949,45 +5949,45 @@
         <v>452.5</v>
       </c>
       <c r="M57">
-        <v>559.0841300000001</v>
+        <v>778.6461760000001</v>
       </c>
       <c r="N57">
-        <v>-106.5841300000001</v>
+        <v>-326.1461760000001</v>
       </c>
       <c r="O57">
-        <v>-26.64603250000002</v>
+        <v>-81.53654400000002</v>
       </c>
       <c r="P57">
-        <v>-79.93809750000005</v>
+        <v>-244.6096320000001</v>
       </c>
       <c r="Q57">
-        <v>-72.93809750000005</v>
+        <v>-237.6096320000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1250789171908766</v>
+        <v>0.1296111350775259</v>
       </c>
       <c r="T57">
-        <v>1.091304136111878</v>
+        <v>1.153691821271001</v>
       </c>
       <c r="U57">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.2023398517858126</v>
+        <v>0.1452842169997378</v>
       </c>
       <c r="W57">
-        <v>0.1170965097578427</v>
+        <v>0.1716269292264527</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.8093594071432504</v>
+        <v>0.581136867998951</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1531399798009249</v>
+        <v>0.1546899798009249</v>
       </c>
       <c r="C58">
-        <v>-1007.012397420356</v>
+        <v>-1113.409684448001</v>
       </c>
       <c r="D58">
-        <v>2610.007602579644</v>
+        <v>2572.855315552</v>
       </c>
       <c r="E58">
-        <v>-2813.98</v>
+        <v>-2744.734999999999</v>
       </c>
       <c r="F58">
-        <v>3877.72</v>
+        <v>3946.965000000001</v>
       </c>
       <c r="G58">
         <v>260.7</v>
@@ -6031,37 +6031,37 @@
         <v>452.5</v>
       </c>
       <c r="M58">
-        <v>778.6461760000001</v>
+        <v>792.5505720000001</v>
       </c>
       <c r="N58">
-        <v>-326.1461760000001</v>
+        <v>-340.0505720000001</v>
       </c>
       <c r="O58">
-        <v>-81.53654400000002</v>
+        <v>-85.01264300000003</v>
       </c>
       <c r="P58">
-        <v>-244.6096320000001</v>
+        <v>-255.0379290000001</v>
       </c>
       <c r="Q58">
-        <v>-237.6096320000001</v>
+        <v>-248.0379290000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1296111350775259</v>
+        <v>0.1315602312421195</v>
       </c>
       <c r="T58">
-        <v>1.153691821271001</v>
+        <v>1.180521863626141</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1452842169997378</v>
+        <v>0.1427353710874616</v>
       </c>
       <c r="W58">
-        <v>0.1716269292264527</v>
+        <v>0.1721387374856377</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.581136867998951</v>
+        <v>0.5709414843498466</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1546899798009249</v>
+        <v>0.1562399798009249</v>
       </c>
       <c r="C59">
-        <v>-1113.409684448001</v>
+        <v>-1218.764123677292</v>
       </c>
       <c r="D59">
-        <v>2572.855315552</v>
+        <v>2536.745876322709</v>
       </c>
       <c r="E59">
-        <v>-2744.734999999999</v>
+        <v>-2675.489999999999</v>
       </c>
       <c r="F59">
-        <v>3946.965000000001</v>
+        <v>4016.21</v>
       </c>
       <c r="G59">
         <v>260.7</v>
@@ -6113,37 +6113,37 @@
         <v>452.5</v>
       </c>
       <c r="M59">
-        <v>792.5505720000001</v>
+        <v>806.4549680000001</v>
       </c>
       <c r="N59">
-        <v>-340.0505720000001</v>
+        <v>-353.9549680000001</v>
       </c>
       <c r="O59">
-        <v>-85.01264300000003</v>
+        <v>-88.48874200000003</v>
       </c>
       <c r="P59">
-        <v>-255.0379290000001</v>
+        <v>-265.4662260000001</v>
       </c>
       <c r="Q59">
-        <v>-248.0379290000001</v>
+        <v>-258.4662260000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1315602312421195</v>
+        <v>0.133602141509789</v>
       </c>
       <c r="T59">
-        <v>1.180521863626141</v>
+        <v>1.208629527045811</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1427353710874616</v>
+        <v>0.1402744164135399</v>
       </c>
       <c r="W59">
-        <v>0.1721387374856377</v>
+        <v>0.1726328971841612</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5709414843498466</v>
+        <v>0.5610976656541595</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1562399798009249</v>
+        <v>0.1577899798009249</v>
       </c>
       <c r="C60">
-        <v>-1218.764123677291</v>
+        <v>-1323.119015788083</v>
       </c>
       <c r="D60">
-        <v>2536.745876322709</v>
+        <v>2501.635984211917</v>
       </c>
       <c r="E60">
-        <v>-2675.49</v>
+        <v>-2606.245</v>
       </c>
       <c r="F60">
-        <v>4016.21</v>
+        <v>4085.455</v>
       </c>
       <c r="G60">
         <v>260.7</v>
@@ -6195,37 +6195,37 @@
         <v>452.5</v>
       </c>
       <c r="M60">
-        <v>806.4549679999999</v>
+        <v>820.359364</v>
       </c>
       <c r="N60">
-        <v>-353.9549679999999</v>
+        <v>-367.859364</v>
       </c>
       <c r="O60">
-        <v>-88.48874199999997</v>
+        <v>-91.96484100000001</v>
       </c>
       <c r="P60">
-        <v>-265.4662259999999</v>
+        <v>-275.894523</v>
       </c>
       <c r="Q60">
-        <v>-258.4662259999999</v>
+        <v>-268.894523</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.133602141509789</v>
+        <v>0.1357436571563692</v>
       </c>
       <c r="T60">
-        <v>1.208629527045811</v>
+        <v>1.238108295998147</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1402744164135399</v>
+        <v>0.1378968839319545</v>
       </c>
       <c r="W60">
-        <v>0.1726328971841612</v>
+        <v>0.1731103057064635</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5610976656541597</v>
+        <v>0.5515875357278179</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1577899798009249</v>
+        <v>0.1593399798009248</v>
       </c>
       <c r="C61">
-        <v>-1323.119015788083</v>
+        <v>-1426.515296969629</v>
       </c>
       <c r="D61">
-        <v>2501.635984211917</v>
+        <v>2467.484703030371</v>
       </c>
       <c r="E61">
-        <v>-2606.245</v>
+        <v>-2537</v>
       </c>
       <c r="F61">
-        <v>4085.455</v>
+        <v>4154.7</v>
       </c>
       <c r="G61">
         <v>260.7</v>
@@ -6277,37 +6277,37 @@
         <v>452.5</v>
       </c>
       <c r="M61">
-        <v>820.359364</v>
+        <v>834.2637599999999</v>
       </c>
       <c r="N61">
-        <v>-367.859364</v>
+        <v>-381.7637599999999</v>
       </c>
       <c r="O61">
-        <v>-91.96484100000001</v>
+        <v>-95.44093999999998</v>
       </c>
       <c r="P61">
-        <v>-275.894523</v>
+        <v>-286.32282</v>
       </c>
       <c r="Q61">
-        <v>-268.894523</v>
+        <v>-279.32282</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1357436571563692</v>
+        <v>0.1379922485852784</v>
       </c>
       <c r="T61">
-        <v>1.238108295998147</v>
+        <v>1.269061003398101</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1378968839319545</v>
+        <v>0.1355986025330886</v>
       </c>
       <c r="W61">
-        <v>0.1731103057064635</v>
+        <v>0.1735718006113558</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5515875357278179</v>
+        <v>0.5423944101323543</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1593399798009248</v>
+        <v>0.1608899798009249</v>
       </c>
       <c r="C62">
-        <v>-1426.515296969629</v>
+        <v>-1528.991698142109</v>
       </c>
       <c r="D62">
-        <v>2467.484703030371</v>
+        <v>2434.253301857891</v>
       </c>
       <c r="E62">
-        <v>-2537</v>
+        <v>-2467.755</v>
       </c>
       <c r="F62">
-        <v>4154.7</v>
+        <v>4223.945</v>
       </c>
       <c r="G62">
         <v>260.7</v>
@@ -6359,37 +6359,37 @@
         <v>452.5</v>
       </c>
       <c r="M62">
-        <v>834.2637599999999</v>
+        <v>848.168156</v>
       </c>
       <c r="N62">
-        <v>-381.7637599999999</v>
+        <v>-395.668156</v>
       </c>
       <c r="O62">
-        <v>-95.44093999999998</v>
+        <v>-98.91703899999999</v>
       </c>
       <c r="P62">
-        <v>-286.32282</v>
+        <v>-296.751117</v>
       </c>
       <c r="Q62">
-        <v>-279.32282</v>
+        <v>-289.751117</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1379922485852784</v>
+        <v>0.1403561523951574</v>
       </c>
       <c r="T62">
-        <v>1.269061003398101</v>
+        <v>1.301601029126258</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1355986025330886</v>
+        <v>0.1333756746227101</v>
       </c>
       <c r="W62">
-        <v>0.1735718006113558</v>
+        <v>0.1740181645357598</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5423944101323543</v>
+        <v>0.5335026984908403</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1608899798009249</v>
+        <v>0.1624399798009249</v>
       </c>
       <c r="C63">
-        <v>-1528.991698142109</v>
+        <v>-1630.584891483014</v>
       </c>
       <c r="D63">
-        <v>2434.253301857891</v>
+        <v>2401.905108516985</v>
       </c>
       <c r="E63">
-        <v>-2467.755</v>
+        <v>-2398.51</v>
       </c>
       <c r="F63">
-        <v>4223.945</v>
+        <v>4293.19</v>
       </c>
       <c r="G63">
         <v>260.7</v>
@@ -6441,37 +6441,37 @@
         <v>452.5</v>
       </c>
       <c r="M63">
-        <v>848.168156</v>
+        <v>862.072552</v>
       </c>
       <c r="N63">
-        <v>-395.668156</v>
+        <v>-409.572552</v>
       </c>
       <c r="O63">
-        <v>-98.91703899999999</v>
+        <v>-102.393138</v>
       </c>
       <c r="P63">
-        <v>-296.751117</v>
+        <v>-307.179414</v>
       </c>
       <c r="Q63">
-        <v>-289.751117</v>
+        <v>-300.179414</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1403561523951574</v>
+        <v>0.1428444721950299</v>
       </c>
       <c r="T63">
-        <v>1.301601029126258</v>
+        <v>1.335853687787475</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1333756746227101</v>
+        <v>0.1312244540642793</v>
       </c>
       <c r="W63">
-        <v>0.1740181645357598</v>
+        <v>0.1744501296238927</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5335026984908403</v>
+        <v>0.5248978162571171</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1624399798009249</v>
+        <v>0.1639899798009249</v>
       </c>
       <c r="C64">
-        <v>-1630.584891483014</v>
+        <v>-1731.329625423847</v>
       </c>
       <c r="D64">
-        <v>2401.905108516985</v>
+        <v>2370.405374576154</v>
       </c>
       <c r="E64">
-        <v>-2398.51</v>
+        <v>-2329.264999999999</v>
       </c>
       <c r="F64">
-        <v>4293.19</v>
+        <v>4362.435</v>
       </c>
       <c r="G64">
         <v>260.7</v>
@@ -6523,37 +6523,37 @@
         <v>452.5</v>
       </c>
       <c r="M64">
-        <v>862.072552</v>
+        <v>875.9769480000001</v>
       </c>
       <c r="N64">
-        <v>-409.572552</v>
+        <v>-423.4769480000001</v>
       </c>
       <c r="O64">
-        <v>-102.393138</v>
+        <v>-105.869237</v>
       </c>
       <c r="P64">
-        <v>-307.179414</v>
+        <v>-317.6077110000001</v>
       </c>
       <c r="Q64">
-        <v>-300.179414</v>
+        <v>-310.6077110000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1428444721950299</v>
+        <v>0.1454672957678686</v>
       </c>
       <c r="T64">
-        <v>1.335853687787475</v>
+        <v>1.371957841511461</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1312244540642793</v>
+        <v>0.1291415262219891</v>
       </c>
       <c r="W64">
-        <v>0.1744501296238927</v>
+        <v>0.1748683815346246</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5248978162571171</v>
+        <v>0.5165661048879564</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1639899798009249</v>
+        <v>0.1655399798009249</v>
       </c>
       <c r="C65">
-        <v>-1731.329625423847</v>
+        <v>-1831.258849161828</v>
       </c>
       <c r="D65">
-        <v>2370.405374576154</v>
+        <v>2339.721150838172</v>
       </c>
       <c r="E65">
-        <v>-2329.264999999999</v>
+        <v>-2260.02</v>
       </c>
       <c r="F65">
-        <v>4362.435</v>
+        <v>4431.68</v>
       </c>
       <c r="G65">
         <v>260.7</v>
@@ -6605,37 +6605,37 @@
         <v>452.5</v>
       </c>
       <c r="M65">
-        <v>875.9769480000001</v>
+        <v>889.8813440000001</v>
       </c>
       <c r="N65">
-        <v>-423.4769480000001</v>
+        <v>-437.3813440000001</v>
       </c>
       <c r="O65">
-        <v>-105.869237</v>
+        <v>-109.345336</v>
       </c>
       <c r="P65">
-        <v>-317.6077110000001</v>
+        <v>-328.0360080000001</v>
       </c>
       <c r="Q65">
-        <v>-310.6077110000001</v>
+        <v>-321.0360080000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1454672957678686</v>
+        <v>0.1482358317614205</v>
       </c>
       <c r="T65">
-        <v>1.371957841511461</v>
+        <v>1.410067781553446</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1291415262219891</v>
+        <v>0.1271236898747705</v>
       </c>
       <c r="W65">
-        <v>0.1748683815346246</v>
+        <v>0.1752735630731461</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5165661048879564</v>
+        <v>0.5084947594990821</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1655399798009249</v>
+        <v>0.1670899798009249</v>
       </c>
       <c r="C66">
-        <v>-1831.258849161828</v>
+        <v>-1930.403827624612</v>
       </c>
       <c r="D66">
-        <v>2339.721150838172</v>
+        <v>2309.821172375388</v>
       </c>
       <c r="E66">
-        <v>-2260.02</v>
+        <v>-2190.775</v>
       </c>
       <c r="F66">
-        <v>4431.68</v>
+        <v>4500.925</v>
       </c>
       <c r="G66">
         <v>260.7</v>
@@ -6687,37 +6687,37 @@
         <v>452.5</v>
       </c>
       <c r="M66">
-        <v>889.8813440000001</v>
+        <v>903.78574</v>
       </c>
       <c r="N66">
-        <v>-437.3813440000001</v>
+        <v>-451.28574</v>
       </c>
       <c r="O66">
-        <v>-109.345336</v>
+        <v>-112.821435</v>
       </c>
       <c r="P66">
-        <v>-328.0360080000001</v>
+        <v>-338.464305</v>
       </c>
       <c r="Q66">
-        <v>-321.0360080000001</v>
+        <v>-331.464305</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1482358317614205</v>
+        <v>0.1511625698117468</v>
       </c>
       <c r="T66">
-        <v>1.410067781553446</v>
+        <v>1.450355432454973</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1271236898747705</v>
+        <v>0.1251679407997741</v>
       </c>
       <c r="W66">
-        <v>0.1752735630731461</v>
+        <v>0.1756662774874054</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5084947594990821</v>
+        <v>0.5006717631990962</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1670899798009249</v>
+        <v>0.1922247538447975</v>
       </c>
       <c r="C67">
-        <v>-1930.403827624612</v>
+        <v>-2396.144855276778</v>
       </c>
       <c r="D67">
-        <v>2309.821172375388</v>
+        <v>1913.325144723222</v>
       </c>
       <c r="E67">
-        <v>-2190.775</v>
+        <v>-2121.53</v>
       </c>
       <c r="F67">
-        <v>4500.925</v>
+        <v>4570.17</v>
       </c>
       <c r="G67">
         <v>260.7</v>
@@ -6769,45 +6769,45 @@
         <v>452.5</v>
       </c>
       <c r="M67">
-        <v>903.78574</v>
+        <v>1077.646086</v>
       </c>
       <c r="N67">
-        <v>-451.28574</v>
+        <v>-625.146086</v>
       </c>
       <c r="O67">
-        <v>-112.821435</v>
+        <v>-156.2865215</v>
       </c>
       <c r="P67">
-        <v>-338.464305</v>
+        <v>-468.8595645</v>
       </c>
       <c r="Q67">
-        <v>-331.464305</v>
+        <v>-461.8595645</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1511625698117468</v>
+        <v>0.155687274935247</v>
       </c>
       <c r="T67">
-        <v>1.450355432454973</v>
+        <v>1.512639701601507</v>
       </c>
       <c r="U67">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1251679407997741</v>
+        <v>0.1049741668156534</v>
       </c>
       <c r="W67">
-        <v>0.1756662774874054</v>
+        <v>0.2110470914648689</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.5006717631990962</v>
+        <v>0.4198966672626138</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1922247538447975</v>
+        <v>0.1941247538447975</v>
       </c>
       <c r="C68">
-        <v>-2396.144855276778</v>
+        <v>-2489.899033149933</v>
       </c>
       <c r="D68">
-        <v>1913.325144723222</v>
+        <v>1888.815966850068</v>
       </c>
       <c r="E68">
-        <v>-2121.53</v>
+        <v>-2052.285</v>
       </c>
       <c r="F68">
-        <v>4570.17</v>
+        <v>4639.415</v>
       </c>
       <c r="G68">
         <v>260.7</v>
@@ -6851,37 +6851,37 @@
         <v>452.5</v>
       </c>
       <c r="M68">
-        <v>1077.646086</v>
+        <v>1093.974057</v>
       </c>
       <c r="N68">
-        <v>-625.146086</v>
+        <v>-641.4740570000001</v>
       </c>
       <c r="O68">
-        <v>-156.2865215</v>
+        <v>-160.36851425</v>
       </c>
       <c r="P68">
-        <v>-468.8595645</v>
+        <v>-481.1055427500001</v>
       </c>
       <c r="Q68">
-        <v>-461.8595645</v>
+        <v>-474.1055427500001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.155687274935247</v>
+        <v>0.1590171923575272</v>
       </c>
       <c r="T68">
-        <v>1.512639701601507</v>
+        <v>1.558477268316705</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1049741668156534</v>
+        <v>0.1034073882064646</v>
       </c>
       <c r="W68">
-        <v>0.2110470914648689</v>
+        <v>0.2114165378609157</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4198966672626138</v>
+        <v>0.4136295528258582</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1941247538447975</v>
+        <v>0.1960247538447975</v>
       </c>
       <c r="C69">
-        <v>-2489.899033149933</v>
+        <v>-2583.033240788262</v>
       </c>
       <c r="D69">
-        <v>1888.815966850068</v>
+        <v>1864.926759211739</v>
       </c>
       <c r="E69">
-        <v>-2052.285</v>
+        <v>-1983.039999999999</v>
       </c>
       <c r="F69">
-        <v>4639.415</v>
+        <v>4708.660000000001</v>
       </c>
       <c r="G69">
         <v>260.7</v>
@@ -6933,37 +6933,37 @@
         <v>452.5</v>
       </c>
       <c r="M69">
-        <v>1093.974057</v>
+        <v>1110.302028</v>
       </c>
       <c r="N69">
-        <v>-641.4740570000001</v>
+        <v>-657.8020280000003</v>
       </c>
       <c r="O69">
-        <v>-160.36851425</v>
+        <v>-164.4505070000001</v>
       </c>
       <c r="P69">
-        <v>-481.1055427500001</v>
+        <v>-493.3515210000002</v>
       </c>
       <c r="Q69">
-        <v>-474.1055427500001</v>
+        <v>-486.3515210000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1590171923575272</v>
+        <v>0.1625552296186999</v>
       </c>
       <c r="T69">
-        <v>1.558477268316705</v>
+        <v>1.607179682951602</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1034073882064646</v>
+        <v>0.1018866913210754</v>
       </c>
       <c r="W69">
-        <v>0.2114165378609157</v>
+        <v>0.2117751181864904</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4136295528258582</v>
+        <v>0.4075467652843014</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1960247538447975</v>
+        <v>0.1979247538447975</v>
       </c>
       <c r="C70">
-        <v>-2583.033240788262</v>
+        <v>-2675.57070800972</v>
       </c>
       <c r="D70">
-        <v>1864.926759211739</v>
+        <v>1841.634291990281</v>
       </c>
       <c r="E70">
-        <v>-1983.039999999999</v>
+        <v>-1913.794999999999</v>
       </c>
       <c r="F70">
-        <v>4708.660000000001</v>
+        <v>4777.905000000001</v>
       </c>
       <c r="G70">
         <v>260.7</v>
@@ -7015,37 +7015,37 @@
         <v>452.5</v>
       </c>
       <c r="M70">
-        <v>1110.302028</v>
+        <v>1126.629999</v>
       </c>
       <c r="N70">
-        <v>-657.8020280000003</v>
+        <v>-674.1299990000002</v>
       </c>
       <c r="O70">
-        <v>-164.4505070000001</v>
+        <v>-168.5324997500001</v>
       </c>
       <c r="P70">
-        <v>-493.3515210000002</v>
+        <v>-505.5974992500002</v>
       </c>
       <c r="Q70">
-        <v>-486.3515210000002</v>
+        <v>-498.5974992500002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1625552296186999</v>
+        <v>0.1663215273483354</v>
       </c>
       <c r="T70">
-        <v>1.607179682951602</v>
+        <v>1.659024188853266</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1018866913210754</v>
+        <v>0.1004100726062772</v>
       </c>
       <c r="W70">
-        <v>0.2117751181864904</v>
+        <v>0.2121233048794398</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4075467652843014</v>
+        <v>0.4016402904251087</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1979247538447975</v>
+        <v>0.1998247538447975</v>
       </c>
       <c r="C71">
-        <v>-2675.57070800972</v>
+        <v>-2767.533518409906</v>
       </c>
       <c r="D71">
-        <v>1841.634291990281</v>
+        <v>1818.916481590095</v>
       </c>
       <c r="E71">
-        <v>-1913.794999999999</v>
+        <v>-1844.549999999999</v>
       </c>
       <c r="F71">
-        <v>4777.905000000001</v>
+        <v>4847.150000000001</v>
       </c>
       <c r="G71">
         <v>260.7</v>
@@ -7097,37 +7097,37 @@
         <v>452.5</v>
       </c>
       <c r="M71">
-        <v>1126.629999</v>
+        <v>1142.95797</v>
       </c>
       <c r="N71">
-        <v>-674.1299990000002</v>
+        <v>-690.4579700000002</v>
       </c>
       <c r="O71">
-        <v>-168.5324997500001</v>
+        <v>-172.6144925</v>
       </c>
       <c r="P71">
-        <v>-505.5974992500002</v>
+        <v>-517.8434775000001</v>
       </c>
       <c r="Q71">
-        <v>-498.5974992500002</v>
+        <v>-510.8434775000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1663215273483354</v>
+        <v>0.1703389115932799</v>
       </c>
       <c r="T71">
-        <v>1.659024188853266</v>
+        <v>1.714324995148375</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1004100726062772</v>
+        <v>0.09897564299761608</v>
       </c>
       <c r="W71">
-        <v>0.2121233048794398</v>
+        <v>0.2124615433811621</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4016402904251087</v>
+        <v>0.3959025719904643</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1998247538447975</v>
+        <v>0.2017247538447975</v>
       </c>
       <c r="C72">
-        <v>-2767.533518409906</v>
+        <v>-2858.942679197751</v>
       </c>
       <c r="D72">
-        <v>1818.916481590095</v>
+        <v>1796.75232080225</v>
       </c>
       <c r="E72">
-        <v>-1844.549999999999</v>
+        <v>-1775.304999999999</v>
       </c>
       <c r="F72">
-        <v>4847.150000000001</v>
+        <v>4916.395</v>
       </c>
       <c r="G72">
         <v>260.7</v>
@@ -7179,37 +7179,37 @@
         <v>452.5</v>
       </c>
       <c r="M72">
-        <v>1142.95797</v>
+        <v>1159.285941</v>
       </c>
       <c r="N72">
-        <v>-690.4579700000002</v>
+        <v>-706.7859410000001</v>
       </c>
       <c r="O72">
-        <v>-172.6144925</v>
+        <v>-176.69648525</v>
       </c>
       <c r="P72">
-        <v>-517.8434775000001</v>
+        <v>-530.0894557500001</v>
       </c>
       <c r="Q72">
-        <v>-510.8434775000001</v>
+        <v>-523.0894557500001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1703389115932799</v>
+        <v>0.1746333568206344</v>
       </c>
       <c r="T72">
-        <v>1.714324995148375</v>
+        <v>1.773439650153492</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09897564299761608</v>
+        <v>0.09758161985680458</v>
       </c>
       <c r="W72">
-        <v>0.2124615433811621</v>
+        <v>0.2127902540377655</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3959025719904643</v>
+        <v>0.3903264794272183</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2017247538447975</v>
+        <v>0.2036247538447974</v>
       </c>
       <c r="C73">
-        <v>-2858.94267919775</v>
+        <v>-2949.818185986826</v>
       </c>
       <c r="D73">
-        <v>1796.75232080225</v>
+        <v>1775.121814013173</v>
       </c>
       <c r="E73">
-        <v>-1775.305</v>
+        <v>-1706.06</v>
       </c>
       <c r="F73">
-        <v>4916.395</v>
+        <v>4985.639999999999</v>
       </c>
       <c r="G73">
         <v>260.7</v>
@@ -7261,37 +7261,37 @@
         <v>452.5</v>
       </c>
       <c r="M73">
-        <v>1159.285941</v>
+        <v>1175.613912</v>
       </c>
       <c r="N73">
-        <v>-706.7859409999999</v>
+        <v>-723.1139119999998</v>
       </c>
       <c r="O73">
-        <v>-176.69648525</v>
+        <v>-180.778478</v>
       </c>
       <c r="P73">
-        <v>-530.0894557499998</v>
+        <v>-542.3354339999999</v>
       </c>
       <c r="Q73">
-        <v>-523.0894557499998</v>
+        <v>-535.3354339999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1746333568206344</v>
+        <v>0.179234548135657</v>
       </c>
       <c r="T73">
-        <v>1.773439650153491</v>
+        <v>1.836776780516115</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09758161985680461</v>
+        <v>0.09622631958101566</v>
       </c>
       <c r="W73">
-        <v>0.2127902540377655</v>
+        <v>0.2131098338427965</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3903264794272184</v>
+        <v>0.3849052783240626</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2036247538447974</v>
+        <v>0.2055247538447974</v>
       </c>
       <c r="C74">
-        <v>-2949.818185986826</v>
+        <v>-3040.179082962334</v>
       </c>
       <c r="D74">
-        <v>1775.121814013173</v>
+        <v>1754.005917037666</v>
       </c>
       <c r="E74">
-        <v>-1706.06</v>
+        <v>-1636.815</v>
       </c>
       <c r="F74">
-        <v>4985.639999999999</v>
+        <v>5054.885</v>
       </c>
       <c r="G74">
         <v>260.7</v>
@@ -7343,37 +7343,37 @@
         <v>452.5</v>
       </c>
       <c r="M74">
-        <v>1175.613912</v>
+        <v>1191.941883</v>
       </c>
       <c r="N74">
-        <v>-723.1139119999998</v>
+        <v>-739.4418830000002</v>
       </c>
       <c r="O74">
-        <v>-180.778478</v>
+        <v>-184.86047075</v>
       </c>
       <c r="P74">
-        <v>-542.3354339999999</v>
+        <v>-554.5814122500001</v>
       </c>
       <c r="Q74">
-        <v>-535.3354339999999</v>
+        <v>-547.5814122500001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.179234548135657</v>
+        <v>0.1841765684369776</v>
       </c>
       <c r="T74">
-        <v>1.836776780516115</v>
+        <v>1.90480555016486</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.09622631958101566</v>
+        <v>0.09490815081963185</v>
       </c>
       <c r="W74">
-        <v>0.2131098338427965</v>
+        <v>0.2134206580367308</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3849052783240626</v>
+        <v>0.3796326032785274</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2055247538447974</v>
+        <v>0.2074247538447975</v>
       </c>
       <c r="C75">
-        <v>-3040.179082962334</v>
+        <v>-3130.043518804271</v>
       </c>
       <c r="D75">
-        <v>1754.005917037666</v>
+        <v>1733.386481195729</v>
       </c>
       <c r="E75">
-        <v>-1636.815</v>
+        <v>-1567.57</v>
       </c>
       <c r="F75">
-        <v>5054.885</v>
+        <v>5124.13</v>
       </c>
       <c r="G75">
         <v>260.7</v>
@@ -7425,37 +7425,37 @@
         <v>452.5</v>
       </c>
       <c r="M75">
-        <v>1191.941883</v>
+        <v>1208.269854</v>
       </c>
       <c r="N75">
-        <v>-739.4418830000002</v>
+        <v>-755.7698540000001</v>
       </c>
       <c r="O75">
-        <v>-184.86047075</v>
+        <v>-188.9424635</v>
       </c>
       <c r="P75">
-        <v>-554.5814122500001</v>
+        <v>-566.8273905000001</v>
       </c>
       <c r="Q75">
-        <v>-547.5814122500001</v>
+        <v>-559.8273905000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1841765684369776</v>
+        <v>0.1894987441460922</v>
       </c>
       <c r="T75">
-        <v>1.90480555016486</v>
+        <v>1.978067302094278</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.09490815081963185</v>
+        <v>0.09362560824098819</v>
       </c>
       <c r="W75">
-        <v>0.2134206580367308</v>
+        <v>0.213723081576775</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3796326032785274</v>
+        <v>0.3745024329639527</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2074247538447975</v>
+        <v>0.2093247538447975</v>
       </c>
       <c r="C76">
-        <v>-3130.043518804271</v>
+        <v>-3219.42879871197</v>
       </c>
       <c r="D76">
-        <v>1733.386481195729</v>
+        <v>1713.24620128803</v>
       </c>
       <c r="E76">
-        <v>-1567.57</v>
+        <v>-1498.325</v>
       </c>
       <c r="F76">
-        <v>5124.13</v>
+        <v>5193.375</v>
       </c>
       <c r="G76">
         <v>260.7</v>
@@ -7507,37 +7507,37 @@
         <v>452.5</v>
       </c>
       <c r="M76">
-        <v>1208.269854</v>
+        <v>1224.597825</v>
       </c>
       <c r="N76">
-        <v>-755.7698540000001</v>
+        <v>-772.0978250000001</v>
       </c>
       <c r="O76">
-        <v>-188.9424635</v>
+        <v>-193.02445625</v>
       </c>
       <c r="P76">
-        <v>-566.8273905000001</v>
+        <v>-579.0733687500001</v>
       </c>
       <c r="Q76">
-        <v>-559.8273905000001</v>
+        <v>-572.0733687500001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1894987441460922</v>
+        <v>0.1952466939119359</v>
       </c>
       <c r="T76">
-        <v>1.978067302094278</v>
+        <v>2.057189994178049</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.09362560824098819</v>
+        <v>0.09237726679777501</v>
       </c>
       <c r="W76">
-        <v>0.213723081576775</v>
+        <v>0.2140174404890847</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3745024329639527</v>
+        <v>0.3695090671911</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2093247538447975</v>
+        <v>0.2112247538447974</v>
       </c>
       <c r="C77">
-        <v>-3219.42879871197</v>
+        <v>-3308.351432843445</v>
       </c>
       <c r="D77">
-        <v>1713.24620128803</v>
+        <v>1693.568567156555</v>
       </c>
       <c r="E77">
-        <v>-1498.325</v>
+        <v>-1429.08</v>
       </c>
       <c r="F77">
-        <v>5193.375</v>
+        <v>5262.62</v>
       </c>
       <c r="G77">
         <v>260.7</v>
@@ -7589,37 +7589,37 @@
         <v>452.5</v>
       </c>
       <c r="M77">
-        <v>1224.597825</v>
+        <v>1240.925796</v>
       </c>
       <c r="N77">
-        <v>-772.0978250000001</v>
+        <v>-788.425796</v>
       </c>
       <c r="O77">
-        <v>-193.02445625</v>
+        <v>-197.106449</v>
       </c>
       <c r="P77">
-        <v>-579.0733687500001</v>
+        <v>-591.319347</v>
       </c>
       <c r="Q77">
-        <v>-572.0733687500001</v>
+        <v>-584.319347</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1952466939119359</v>
+        <v>0.2014736394915999</v>
       </c>
       <c r="T77">
-        <v>2.057189994178049</v>
+        <v>2.142906243935468</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09237726679777501</v>
+        <v>0.09116177644517272</v>
       </c>
       <c r="W77">
-        <v>0.2140174404890847</v>
+        <v>0.2143040531142283</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3695090671911</v>
+        <v>0.3646471057806908</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2112247538447974</v>
+        <v>0.2131247538447975</v>
       </c>
       <c r="C78">
-        <v>-3308.351432843445</v>
+        <v>-3396.82718145451</v>
       </c>
       <c r="D78">
-        <v>1693.568567156555</v>
+        <v>1674.33781854549</v>
       </c>
       <c r="E78">
-        <v>-1429.08</v>
+        <v>-1359.835</v>
       </c>
       <c r="F78">
-        <v>5262.62</v>
+        <v>5331.865</v>
       </c>
       <c r="G78">
         <v>260.7</v>
@@ -7671,37 +7671,37 @@
         <v>452.5</v>
       </c>
       <c r="M78">
-        <v>1240.925796</v>
+        <v>1257.253767</v>
       </c>
       <c r="N78">
-        <v>-788.425796</v>
+        <v>-804.7537669999999</v>
       </c>
       <c r="O78">
-        <v>-197.106449</v>
+        <v>-201.18844175</v>
       </c>
       <c r="P78">
-        <v>-591.319347</v>
+        <v>-603.5653252499999</v>
       </c>
       <c r="Q78">
-        <v>-584.319347</v>
+        <v>-596.5653252499999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2014736394915999</v>
+        <v>0.2082420585999303</v>
       </c>
       <c r="T78">
-        <v>2.142906243935468</v>
+        <v>2.236076080628314</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09116177644517272</v>
+        <v>0.08997785727056008</v>
       </c>
       <c r="W78">
-        <v>0.2143040531142283</v>
+        <v>0.2145832212556019</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3646471057806908</v>
+        <v>0.3599114290822404</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2131247538447975</v>
+        <v>0.2150247538447975</v>
       </c>
       <c r="C79">
-        <v>-3396.82718145451</v>
+        <v>-3484.871096997056</v>
       </c>
       <c r="D79">
-        <v>1674.33781854549</v>
+        <v>1655.538903002944</v>
       </c>
       <c r="E79">
-        <v>-1359.835</v>
+        <v>-1290.589999999999</v>
       </c>
       <c r="F79">
-        <v>5331.865</v>
+        <v>5401.110000000001</v>
       </c>
       <c r="G79">
         <v>260.7</v>
@@ -7753,37 +7753,37 @@
         <v>452.5</v>
       </c>
       <c r="M79">
-        <v>1257.253767</v>
+        <v>1273.581738</v>
       </c>
       <c r="N79">
-        <v>-804.7537669999999</v>
+        <v>-821.0817380000001</v>
       </c>
       <c r="O79">
-        <v>-201.18844175</v>
+        <v>-205.2704345</v>
       </c>
       <c r="P79">
-        <v>-603.5653252499999</v>
+        <v>-615.8113035000001</v>
       </c>
       <c r="Q79">
-        <v>-596.5653252499999</v>
+        <v>-608.8113035000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2082420585999303</v>
+        <v>0.2156257885362907</v>
       </c>
       <c r="T79">
-        <v>2.236076080628314</v>
+        <v>2.337715902475056</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08997785727056008</v>
+        <v>0.08882429499786058</v>
       </c>
       <c r="W79">
-        <v>0.2145832212556019</v>
+        <v>0.2148552312395045</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3599114290822404</v>
+        <v>0.3552971799914424</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2150247538447975</v>
+        <v>0.2169247538447975</v>
       </c>
       <c r="C80">
-        <v>-3484.871096997056</v>
+        <v>-3572.49756341283</v>
       </c>
       <c r="D80">
-        <v>1655.538903002944</v>
+        <v>1637.157436587171</v>
       </c>
       <c r="E80">
-        <v>-1290.589999999999</v>
+        <v>-1221.344999999999</v>
       </c>
       <c r="F80">
-        <v>5401.110000000001</v>
+        <v>5470.355</v>
       </c>
       <c r="G80">
         <v>260.7</v>
@@ -7835,37 +7835,37 @@
         <v>452.5</v>
       </c>
       <c r="M80">
-        <v>1273.581738</v>
+        <v>1289.909709</v>
       </c>
       <c r="N80">
-        <v>-821.0817380000001</v>
+        <v>-837.4097090000002</v>
       </c>
       <c r="O80">
-        <v>-205.2704345</v>
+        <v>-209.3524272500001</v>
       </c>
       <c r="P80">
-        <v>-615.8113035000001</v>
+        <v>-628.0572817500001</v>
       </c>
       <c r="Q80">
-        <v>-608.8113035000001</v>
+        <v>-621.0572817500001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2156257885362907</v>
+        <v>0.2237127308475428</v>
       </c>
       <c r="T80">
-        <v>2.337715902475056</v>
+        <v>2.449035707354822</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08882429499786058</v>
+        <v>0.08769993683333069</v>
       </c>
       <c r="W80">
-        <v>0.2148552312395045</v>
+        <v>0.2151203548947006</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3552971799914424</v>
+        <v>0.3507997473333228</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2169247538447975</v>
+        <v>0.2188247538447975</v>
       </c>
       <c r="C81">
-        <v>-3572.49756341283</v>
+        <v>-3659.720332838271</v>
       </c>
       <c r="D81">
-        <v>1637.157436587171</v>
+        <v>1619.179667161729</v>
       </c>
       <c r="E81">
-        <v>-1221.344999999999</v>
+        <v>-1152.099999999999</v>
       </c>
       <c r="F81">
-        <v>5470.355</v>
+        <v>5539.6</v>
       </c>
       <c r="G81">
         <v>260.7</v>
@@ -7917,37 +7917,37 @@
         <v>452.5</v>
       </c>
       <c r="M81">
-        <v>1289.909709</v>
+        <v>1306.23768</v>
       </c>
       <c r="N81">
-        <v>-837.4097090000002</v>
+        <v>-853.7376800000002</v>
       </c>
       <c r="O81">
-        <v>-209.3524272500001</v>
+        <v>-213.43442</v>
       </c>
       <c r="P81">
-        <v>-628.0572817500001</v>
+        <v>-640.3032600000001</v>
       </c>
       <c r="Q81">
-        <v>-621.0572817500001</v>
+        <v>-633.3032600000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2237127308475428</v>
+        <v>0.2326083673899199</v>
       </c>
       <c r="T81">
-        <v>2.449035707354822</v>
+        <v>2.571487492722562</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08769993683333069</v>
+        <v>0.08660368762291407</v>
       </c>
       <c r="W81">
-        <v>0.2151203548947006</v>
+        <v>0.2153788504585169</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3507997473333228</v>
+        <v>0.3464147504916563</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2188247538447975</v>
+        <v>0.2207247538447975</v>
       </c>
       <c r="C82">
-        <v>-3659.720332838271</v>
+        <v>-3746.552559917273</v>
       </c>
       <c r="D82">
-        <v>1619.179667161729</v>
+        <v>1601.592440082727</v>
       </c>
       <c r="E82">
-        <v>-1152.099999999999</v>
+        <v>-1082.855</v>
       </c>
       <c r="F82">
-        <v>5539.6</v>
+        <v>5608.845</v>
       </c>
       <c r="G82">
         <v>260.7</v>
@@ -7999,37 +7999,37 @@
         <v>452.5</v>
       </c>
       <c r="M82">
-        <v>1306.23768</v>
+        <v>1322.565651</v>
       </c>
       <c r="N82">
-        <v>-853.7376800000002</v>
+        <v>-870.0656510000001</v>
       </c>
       <c r="O82">
-        <v>-213.43442</v>
+        <v>-217.51641275</v>
       </c>
       <c r="P82">
-        <v>-640.3032600000001</v>
+        <v>-652.5492382500001</v>
       </c>
       <c r="Q82">
-        <v>-633.3032600000001</v>
+        <v>-645.5492382500001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2326083673899199</v>
+        <v>0.2424403867262314</v>
       </c>
       <c r="T82">
-        <v>2.571487492722562</v>
+        <v>2.706828939707961</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08660368762291407</v>
+        <v>0.08553450629423612</v>
       </c>
       <c r="W82">
-        <v>0.2153788504585169</v>
+        <v>0.2156309634158191</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3464147504916563</v>
+        <v>0.3421380251769445</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2207247538447975</v>
+        <v>0.2226247538447975</v>
       </c>
       <c r="C83">
-        <v>-3746.552559917273</v>
+        <v>-3833.006833901775</v>
       </c>
       <c r="D83">
-        <v>1601.592440082727</v>
+        <v>1584.383166098225</v>
       </c>
       <c r="E83">
-        <v>-1082.855</v>
+        <v>-1013.61</v>
       </c>
       <c r="F83">
-        <v>5608.845</v>
+        <v>5678.09</v>
       </c>
       <c r="G83">
         <v>260.7</v>
@@ -8081,37 +8081,37 @@
         <v>452.5</v>
       </c>
       <c r="M83">
-        <v>1322.565651</v>
+        <v>1338.893622</v>
       </c>
       <c r="N83">
-        <v>-870.0656510000001</v>
+        <v>-886.3936220000001</v>
       </c>
       <c r="O83">
-        <v>-217.51641275</v>
+        <v>-221.5984055</v>
       </c>
       <c r="P83">
-        <v>-652.5492382500001</v>
+        <v>-664.7952165</v>
       </c>
       <c r="Q83">
-        <v>-645.5492382500001</v>
+        <v>-657.7952165</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2424403867262314</v>
+        <v>0.2533648526554665</v>
       </c>
       <c r="T83">
-        <v>2.706828939707961</v>
+        <v>2.857208325247292</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08553450629423612</v>
+        <v>0.08449140255894055</v>
       </c>
       <c r="W83">
-        <v>0.2156309634158191</v>
+        <v>0.2158769272766018</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3421380251769445</v>
+        <v>0.3379656102357622</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2226247538447975</v>
+        <v>0.2245247538447975</v>
       </c>
       <c r="C84">
-        <v>-3833.006833901775</v>
+        <v>-3919.095208704804</v>
       </c>
       <c r="D84">
-        <v>1584.383166098225</v>
+        <v>1567.539791295197</v>
       </c>
       <c r="E84">
-        <v>-1013.61</v>
+        <v>-944.3649999999989</v>
       </c>
       <c r="F84">
-        <v>5678.09</v>
+        <v>5747.335000000001</v>
       </c>
       <c r="G84">
         <v>260.7</v>
@@ -8163,37 +8163,37 @@
         <v>452.5</v>
       </c>
       <c r="M84">
-        <v>1338.893622</v>
+        <v>1355.221593</v>
       </c>
       <c r="N84">
-        <v>-886.3936220000001</v>
+        <v>-902.7215930000002</v>
       </c>
       <c r="O84">
-        <v>-221.5984055</v>
+        <v>-225.6803982500001</v>
       </c>
       <c r="P84">
-        <v>-664.7952165</v>
+        <v>-677.0411947500002</v>
       </c>
       <c r="Q84">
-        <v>-657.7952165</v>
+        <v>-670.0411947500002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2533648526554665</v>
+        <v>0.265574549870494</v>
       </c>
       <c r="T84">
-        <v>2.857208325247292</v>
+        <v>3.025279403203015</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08449140255894055</v>
+        <v>0.08347343385341115</v>
       </c>
       <c r="W84">
-        <v>0.2158769272766018</v>
+        <v>0.2161169642973657</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3379656102357622</v>
+        <v>0.3338937354136445</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2245247538447975</v>
+        <v>0.2264247538447975</v>
       </c>
       <c r="C85">
-        <v>-3919.095208704804</v>
+        <v>-4004.829231056746</v>
       </c>
       <c r="D85">
-        <v>1567.539791295197</v>
+        <v>1551.050768943255</v>
       </c>
       <c r="E85">
-        <v>-944.3649999999989</v>
+        <v>-875.119999999999</v>
       </c>
       <c r="F85">
-        <v>5747.335000000001</v>
+        <v>5816.580000000001</v>
       </c>
       <c r="G85">
         <v>260.7</v>
@@ -8245,37 +8245,37 @@
         <v>452.5</v>
       </c>
       <c r="M85">
-        <v>1355.221593</v>
+        <v>1371.549564</v>
       </c>
       <c r="N85">
-        <v>-902.7215930000002</v>
+        <v>-919.0495640000001</v>
       </c>
       <c r="O85">
-        <v>-225.6803982500001</v>
+        <v>-229.762391</v>
       </c>
       <c r="P85">
-        <v>-677.0411947500002</v>
+        <v>-689.2871730000002</v>
       </c>
       <c r="Q85">
-        <v>-670.0411947500002</v>
+        <v>-682.2871730000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.265574549870494</v>
+        <v>0.2793104592373999</v>
       </c>
       <c r="T85">
-        <v>3.025279403203015</v>
+        <v>3.214359365903204</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08347343385341115</v>
+        <v>0.0824797024980134</v>
       </c>
       <c r="W85">
-        <v>0.2161169642973657</v>
+        <v>0.2163512861509685</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3338937354136445</v>
+        <v>0.3299188099920536</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2264247538447975</v>
+        <v>0.2283247538447974</v>
       </c>
       <c r="C86">
-        <v>-4004.829231056744</v>
+        <v>-4090.219966903062</v>
       </c>
       <c r="D86">
-        <v>1551.050768943256</v>
+        <v>1534.905033096938</v>
       </c>
       <c r="E86">
-        <v>-875.1199999999999</v>
+        <v>-805.875</v>
       </c>
       <c r="F86">
-        <v>5816.58</v>
+        <v>5885.825</v>
       </c>
       <c r="G86">
         <v>260.7</v>
@@ -8327,37 +8327,37 @@
         <v>452.5</v>
       </c>
       <c r="M86">
-        <v>1371.549564</v>
+        <v>1387.877535</v>
       </c>
       <c r="N86">
-        <v>-919.0495640000001</v>
+        <v>-935.3775350000001</v>
       </c>
       <c r="O86">
-        <v>-229.762391</v>
+        <v>-233.84438375</v>
       </c>
       <c r="P86">
-        <v>-689.2871730000002</v>
+        <v>-701.5331512500001</v>
       </c>
       <c r="Q86">
-        <v>-682.2871730000002</v>
+        <v>-694.5331512500001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2793104592373997</v>
+        <v>0.2948778231865598</v>
       </c>
       <c r="T86">
-        <v>3.214359365903202</v>
+        <v>3.428649990296749</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0824797024980134</v>
+        <v>0.0815093530568603</v>
       </c>
       <c r="W86">
-        <v>0.2163512861509685</v>
+        <v>0.2165800945491924</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3299188099920536</v>
+        <v>0.3260374122274412</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2283247538447974</v>
+        <v>0.2302247538447975</v>
       </c>
       <c r="C87">
-        <v>-4090.219966903062</v>
+        <v>-4175.278026170249</v>
       </c>
       <c r="D87">
-        <v>1534.905033096938</v>
+        <v>1519.091973829751</v>
       </c>
       <c r="E87">
-        <v>-805.875</v>
+        <v>-736.6300000000001</v>
       </c>
       <c r="F87">
-        <v>5885.825</v>
+        <v>5955.07</v>
       </c>
       <c r="G87">
         <v>260.7</v>
@@ -8409,37 +8409,37 @@
         <v>452.5</v>
       </c>
       <c r="M87">
-        <v>1387.877535</v>
+        <v>1404.205506</v>
       </c>
       <c r="N87">
-        <v>-935.3775350000001</v>
+        <v>-951.705506</v>
       </c>
       <c r="O87">
-        <v>-233.84438375</v>
+        <v>-237.9263765</v>
       </c>
       <c r="P87">
-        <v>-701.5331512500001</v>
+        <v>-713.7791295</v>
       </c>
       <c r="Q87">
-        <v>-694.5331512500001</v>
+        <v>-706.7791295</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2948778231865598</v>
+        <v>0.312669096271314</v>
       </c>
       <c r="T87">
-        <v>3.428649990296749</v>
+        <v>3.673553561032231</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0815093530568603</v>
+        <v>0.08056156988178054</v>
       </c>
       <c r="W87">
-        <v>0.2165800945491924</v>
+        <v>0.2168035818218761</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3260374122274412</v>
+        <v>0.3222462795271221</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2302247538447975</v>
+        <v>0.2321247538447975</v>
       </c>
       <c r="C88">
-        <v>-4175.278026170249</v>
+        <v>-4260.01358601653</v>
       </c>
       <c r="D88">
-        <v>1519.091973829751</v>
+        <v>1503.601413983469</v>
       </c>
       <c r="E88">
-        <v>-736.6300000000001</v>
+        <v>-667.3850000000002</v>
       </c>
       <c r="F88">
-        <v>5955.07</v>
+        <v>6024.315</v>
       </c>
       <c r="G88">
         <v>260.7</v>
@@ -8491,37 +8491,37 @@
         <v>452.5</v>
       </c>
       <c r="M88">
-        <v>1404.205506</v>
+        <v>1420.533477</v>
       </c>
       <c r="N88">
-        <v>-951.705506</v>
+        <v>-968.0334769999999</v>
       </c>
       <c r="O88">
-        <v>-237.9263765</v>
+        <v>-242.00836925</v>
       </c>
       <c r="P88">
-        <v>-713.7791295</v>
+        <v>-726.02510775</v>
       </c>
       <c r="Q88">
-        <v>-706.7791295</v>
+        <v>-719.02510775</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.312669096271314</v>
+        <v>0.3331974882921843</v>
       </c>
       <c r="T88">
-        <v>3.673553561032231</v>
+        <v>3.956134604188557</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08056156988178054</v>
+        <v>0.07963557482566812</v>
       </c>
       <c r="W88">
-        <v>0.2168035818218761</v>
+        <v>0.2170219314561075</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3222462795271221</v>
+        <v>0.3185422993026725</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2321247538447975</v>
+        <v>0.2340247538447975</v>
       </c>
       <c r="C89">
-        <v>-4260.01358601653</v>
+        <v>-4344.436412674358</v>
       </c>
       <c r="D89">
-        <v>1503.601413983469</v>
+        <v>1488.423587325643</v>
       </c>
       <c r="E89">
-        <v>-667.3850000000002</v>
+        <v>-598.1399999999994</v>
       </c>
       <c r="F89">
-        <v>6024.315</v>
+        <v>6093.56</v>
       </c>
       <c r="G89">
         <v>260.7</v>
@@ -8573,37 +8573,37 @@
         <v>452.5</v>
       </c>
       <c r="M89">
-        <v>1420.533477</v>
+        <v>1436.861448</v>
       </c>
       <c r="N89">
-        <v>-968.0334769999999</v>
+        <v>-984.3614480000001</v>
       </c>
       <c r="O89">
-        <v>-242.00836925</v>
+        <v>-246.090362</v>
       </c>
       <c r="P89">
-        <v>-726.02510775</v>
+        <v>-738.2710860000001</v>
       </c>
       <c r="Q89">
-        <v>-719.02510775</v>
+        <v>-731.2710860000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3331974882921843</v>
+        <v>0.3571472789831997</v>
       </c>
       <c r="T89">
-        <v>3.956134604188557</v>
+        <v>4.285812487870936</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07963557482566812</v>
+        <v>0.07873062511174006</v>
       </c>
       <c r="W89">
-        <v>0.2170219314561075</v>
+        <v>0.2172353185986517</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3185422993026725</v>
+        <v>0.3149225004469602</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2340247538447975</v>
+        <v>0.2359247538447974</v>
       </c>
       <c r="C90">
-        <v>-4344.436412674358</v>
+        <v>-4428.555881983217</v>
       </c>
       <c r="D90">
-        <v>1488.423587325643</v>
+        <v>1473.549118016783</v>
       </c>
       <c r="E90">
-        <v>-598.1399999999994</v>
+        <v>-528.8949999999995</v>
       </c>
       <c r="F90">
-        <v>6093.56</v>
+        <v>6162.805</v>
       </c>
       <c r="G90">
         <v>260.7</v>
@@ -8655,37 +8655,37 @@
         <v>452.5</v>
       </c>
       <c r="M90">
-        <v>1436.861448</v>
+        <v>1453.189419</v>
       </c>
       <c r="N90">
-        <v>-984.3614480000001</v>
+        <v>-1000.689419</v>
       </c>
       <c r="O90">
-        <v>-246.090362</v>
+        <v>-250.17235475</v>
       </c>
       <c r="P90">
-        <v>-738.2710860000001</v>
+        <v>-750.51706425</v>
       </c>
       <c r="Q90">
-        <v>-731.2710860000001</v>
+        <v>-743.51706425</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3571472789831997</v>
+        <v>0.3854515770725815</v>
       </c>
       <c r="T90">
-        <v>4.285812487870936</v>
+        <v>4.675431804950112</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07873062511174006</v>
+        <v>0.07784601134643962</v>
       </c>
       <c r="W90">
-        <v>0.2172353185986517</v>
+        <v>0.2174439105245095</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3149225004469602</v>
+        <v>0.3113840453857585</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2359247538447974</v>
+        <v>0.2378247538447975</v>
       </c>
       <c r="C91">
-        <v>-4428.555881983217</v>
+        <v>-4512.380998703453</v>
       </c>
       <c r="D91">
-        <v>1473.549118016783</v>
+        <v>1458.969001296548</v>
       </c>
       <c r="E91">
-        <v>-528.8949999999995</v>
+        <v>-459.6499999999996</v>
       </c>
       <c r="F91">
-        <v>6162.805</v>
+        <v>6232.05</v>
       </c>
       <c r="G91">
         <v>260.7</v>
@@ -8737,37 +8737,37 @@
         <v>452.5</v>
       </c>
       <c r="M91">
-        <v>1453.189419</v>
+        <v>1469.51739</v>
       </c>
       <c r="N91">
-        <v>-1000.689419</v>
+        <v>-1017.01739</v>
       </c>
       <c r="O91">
-        <v>-250.17235475</v>
+        <v>-254.2543475000001</v>
       </c>
       <c r="P91">
-        <v>-750.51706425</v>
+        <v>-762.7630425000002</v>
       </c>
       <c r="Q91">
-        <v>-743.51706425</v>
+        <v>-755.7630425000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3854515770725815</v>
+        <v>0.4194167347798397</v>
       </c>
       <c r="T91">
-        <v>4.675431804950112</v>
+        <v>5.142974985445124</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07784601134643962</v>
+        <v>0.0769810556648125</v>
       </c>
       <c r="W91">
-        <v>0.2174439105245095</v>
+        <v>0.2176478670742372</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3113840453857585</v>
+        <v>0.30792422265925</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2378247538447975</v>
+        <v>0.2397247538447975</v>
       </c>
       <c r="C92">
-        <v>-4512.380998703453</v>
+        <v>-4595.92041469473</v>
       </c>
       <c r="D92">
-        <v>1458.969001296548</v>
+        <v>1444.67458530527</v>
       </c>
       <c r="E92">
-        <v>-459.6499999999996</v>
+        <v>-390.4049999999997</v>
       </c>
       <c r="F92">
-        <v>6232.05</v>
+        <v>6301.295</v>
       </c>
       <c r="G92">
         <v>260.7</v>
@@ -8819,37 +8819,37 @@
         <v>452.5</v>
       </c>
       <c r="M92">
-        <v>1469.51739</v>
+        <v>1485.845361</v>
       </c>
       <c r="N92">
-        <v>-1017.01739</v>
+        <v>-1033.345361</v>
       </c>
       <c r="O92">
-        <v>-254.2543475000001</v>
+        <v>-258.33634025</v>
       </c>
       <c r="P92">
-        <v>-762.7630425000002</v>
+        <v>-775.0090207500001</v>
       </c>
       <c r="Q92">
-        <v>-755.7630425000002</v>
+        <v>-768.0090207500001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4194167347798397</v>
+        <v>0.4609297053109331</v>
       </c>
       <c r="T92">
-        <v>5.142974985445124</v>
+        <v>5.714416650494584</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0769810556648125</v>
+        <v>0.07613510999816621</v>
       </c>
       <c r="W92">
-        <v>0.2176478670742372</v>
+        <v>0.2178473410624324</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.30792422265925</v>
+        <v>0.3045404399926649</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2397247538447975</v>
+        <v>0.2416247538447975</v>
       </c>
       <c r="C93">
-        <v>-4595.92041469473</v>
+        <v>-4679.182446036209</v>
       </c>
       <c r="D93">
-        <v>1444.67458530527</v>
+        <v>1430.657553963792</v>
       </c>
       <c r="E93">
-        <v>-390.4049999999997</v>
+        <v>-321.1599999999999</v>
       </c>
       <c r="F93">
-        <v>6301.295</v>
+        <v>6370.54</v>
       </c>
       <c r="G93">
         <v>260.7</v>
@@ -8901,37 +8901,37 @@
         <v>452.5</v>
       </c>
       <c r="M93">
-        <v>1485.845361</v>
+        <v>1502.173332</v>
       </c>
       <c r="N93">
-        <v>-1033.345361</v>
+        <v>-1049.673332</v>
       </c>
       <c r="O93">
-        <v>-258.33634025</v>
+        <v>-262.418333</v>
       </c>
       <c r="P93">
-        <v>-775.0090207500001</v>
+        <v>-787.254999</v>
       </c>
       <c r="Q93">
-        <v>-768.0090207500001</v>
+        <v>-780.254999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4609297053109331</v>
+        <v>0.5128209184747998</v>
       </c>
       <c r="T93">
-        <v>5.714416650494584</v>
+        <v>6.428718731806408</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07613510999816621</v>
+        <v>0.0753075544547079</v>
       </c>
       <c r="W93">
-        <v>0.2178473410624324</v>
+        <v>0.2180424786595799</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3045404399926649</v>
+        <v>0.3012302178188315</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2416247538447975</v>
+        <v>0.2435247538447974</v>
       </c>
       <c r="C94">
-        <v>-4679.182446036209</v>
+        <v>-4762.175089159664</v>
       </c>
       <c r="D94">
-        <v>1430.657553963792</v>
+        <v>1416.909910840336</v>
       </c>
       <c r="E94">
-        <v>-321.1599999999999</v>
+        <v>-251.9149999999991</v>
       </c>
       <c r="F94">
-        <v>6370.54</v>
+        <v>6439.785000000001</v>
       </c>
       <c r="G94">
         <v>260.7</v>
@@ -8983,37 +8983,37 @@
         <v>452.5</v>
       </c>
       <c r="M94">
-        <v>1502.173332</v>
+        <v>1518.501303</v>
       </c>
       <c r="N94">
-        <v>-1049.673332</v>
+        <v>-1066.001303</v>
       </c>
       <c r="O94">
-        <v>-262.418333</v>
+        <v>-266.5003257500001</v>
       </c>
       <c r="P94">
-        <v>-787.254999</v>
+        <v>-799.5009772500002</v>
       </c>
       <c r="Q94">
-        <v>-780.254999</v>
+        <v>-792.5009772500002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5128209184747998</v>
+        <v>0.5795381925426284</v>
       </c>
       <c r="T94">
-        <v>6.428718731806408</v>
+        <v>7.347107122064467</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0753075544547079</v>
+        <v>0.07449779580465726</v>
       </c>
       <c r="W94">
-        <v>0.2180424786595799</v>
+        <v>0.2182334197492618</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3012302178188315</v>
+        <v>0.2979911832186291</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2435247538447974</v>
+        <v>0.2454247538447975</v>
       </c>
       <c r="C95">
-        <v>-4762.175089159664</v>
+        <v>-4844.906036061269</v>
       </c>
       <c r="D95">
-        <v>1416.909910840336</v>
+        <v>1403.423963938732</v>
       </c>
       <c r="E95">
-        <v>-251.9149999999991</v>
+        <v>-182.6699999999992</v>
       </c>
       <c r="F95">
-        <v>6439.785000000001</v>
+        <v>6509.030000000001</v>
       </c>
       <c r="G95">
         <v>260.7</v>
@@ -9065,37 +9065,37 @@
         <v>452.5</v>
       </c>
       <c r="M95">
-        <v>1518.501303</v>
+        <v>1534.829274</v>
       </c>
       <c r="N95">
-        <v>-1066.001303</v>
+        <v>-1082.329274</v>
       </c>
       <c r="O95">
-        <v>-266.5003257500001</v>
+        <v>-270.5823185</v>
       </c>
       <c r="P95">
-        <v>-799.5009772500002</v>
+        <v>-811.7469555000001</v>
       </c>
       <c r="Q95">
-        <v>-792.5009772500002</v>
+        <v>-804.7469555000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5795381925426284</v>
+        <v>0.6684945579664</v>
       </c>
       <c r="T95">
-        <v>7.347107122064467</v>
+        <v>8.571624975741882</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07449779580465726</v>
+        <v>0.07370526606205452</v>
       </c>
       <c r="W95">
-        <v>0.2182334197492618</v>
+        <v>0.2184202982625676</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2979911832186291</v>
+        <v>0.2948210642482181</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2454247538447975</v>
+        <v>0.2473247538447975</v>
       </c>
       <c r="C96">
-        <v>-4844.906036061269</v>
+        <v>-4927.382688652876</v>
       </c>
       <c r="D96">
-        <v>1403.423963938732</v>
+        <v>1390.192311347125</v>
       </c>
       <c r="E96">
-        <v>-182.6699999999992</v>
+        <v>-113.4249999999993</v>
       </c>
       <c r="F96">
-        <v>6509.030000000001</v>
+        <v>6578.275000000001</v>
       </c>
       <c r="G96">
         <v>260.7</v>
@@ -9147,37 +9147,37 @@
         <v>452.5</v>
       </c>
       <c r="M96">
-        <v>1534.829274</v>
+        <v>1551.157245</v>
       </c>
       <c r="N96">
-        <v>-1082.329274</v>
+        <v>-1098.657245</v>
       </c>
       <c r="O96">
-        <v>-270.5823185</v>
+        <v>-274.66431125</v>
       </c>
       <c r="P96">
-        <v>-811.7469555000001</v>
+        <v>-823.99293375</v>
       </c>
       <c r="Q96">
-        <v>-804.7469555000001</v>
+        <v>-816.99293375</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6684945579664</v>
+        <v>0.7930334695596803</v>
       </c>
       <c r="T96">
-        <v>8.571624975741882</v>
+        <v>10.28594997089026</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07370526606205452</v>
+        <v>0.07292942115613817</v>
       </c>
       <c r="W96">
-        <v>0.2184202982625676</v>
+        <v>0.2186032424913826</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2948210642482181</v>
+        <v>0.2917176846245526</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2473247538447975</v>
+        <v>0.2492247538447975</v>
       </c>
       <c r="C97">
-        <v>-4927.382688652876</v>
+        <v>-5009.612172309052</v>
       </c>
       <c r="D97">
-        <v>1390.192311347125</v>
+        <v>1377.207827690949</v>
       </c>
       <c r="E97">
-        <v>-113.4249999999993</v>
+        <v>-44.17999999999938</v>
       </c>
       <c r="F97">
-        <v>6578.275000000001</v>
+        <v>6647.52</v>
       </c>
       <c r="G97">
         <v>260.7</v>
@@ -9229,37 +9229,37 @@
         <v>452.5</v>
       </c>
       <c r="M97">
-        <v>1551.157245</v>
+        <v>1567.485216</v>
       </c>
       <c r="N97">
-        <v>-1098.657245</v>
+        <v>-1114.985216</v>
       </c>
       <c r="O97">
-        <v>-274.66431125</v>
+        <v>-278.7463040000001</v>
       </c>
       <c r="P97">
-        <v>-823.99293375</v>
+        <v>-836.2389120000003</v>
       </c>
       <c r="Q97">
-        <v>-816.99293375</v>
+        <v>-829.2389120000003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7930334695596803</v>
+        <v>0.9798418369496009</v>
       </c>
       <c r="T97">
-        <v>10.28594997089026</v>
+        <v>12.85743746361283</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07292942115613817</v>
+        <v>0.07216973968576172</v>
       </c>
       <c r="W97">
-        <v>0.2186032424913826</v>
+        <v>0.2187823753820974</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2917176846245526</v>
+        <v>0.2886789587430468</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2492247538447975</v>
+        <v>0.2511247538447975</v>
       </c>
       <c r="C98">
-        <v>-5009.612172309052</v>
+        <v>-5091.601348661947</v>
       </c>
       <c r="D98">
-        <v>1377.207827690948</v>
+        <v>1364.463651338053</v>
       </c>
       <c r="E98">
-        <v>-44.18000000000029</v>
+        <v>25.0649999999996</v>
       </c>
       <c r="F98">
-        <v>6647.52</v>
+        <v>6716.764999999999</v>
       </c>
       <c r="G98">
         <v>260.7</v>
@@ -9311,37 +9311,37 @@
         <v>452.5</v>
       </c>
       <c r="M98">
-        <v>1567.485216</v>
+        <v>1583.813187</v>
       </c>
       <c r="N98">
-        <v>-1114.985216</v>
+        <v>-1131.313187</v>
       </c>
       <c r="O98">
-        <v>-278.746304</v>
+        <v>-282.82829675</v>
       </c>
       <c r="P98">
-        <v>-836.238912</v>
+        <v>-848.48489025</v>
       </c>
       <c r="Q98">
-        <v>-829.238912</v>
+        <v>-841.48489025</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9798418369495984</v>
+        <v>1.291189115932798</v>
       </c>
       <c r="T98">
-        <v>12.8574374636128</v>
+        <v>17.14324995148373</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07216973968576174</v>
+        <v>0.07142572175085697</v>
       </c>
       <c r="W98">
-        <v>0.2187823753820974</v>
+        <v>0.218957814811148</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2886789587430469</v>
+        <v>0.2857028870034279</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2511247538447975</v>
+        <v>0.2530247538447975</v>
       </c>
       <c r="C99">
-        <v>-5091.601348661947</v>
+        <v>-5173.356827692285</v>
       </c>
       <c r="D99">
-        <v>1364.463651338053</v>
+        <v>1351.953172307715</v>
       </c>
       <c r="E99">
-        <v>25.0649999999996</v>
+        <v>94.3100000000004</v>
       </c>
       <c r="F99">
-        <v>6716.764999999999</v>
+        <v>6786.01</v>
       </c>
       <c r="G99">
         <v>260.7</v>
@@ -9393,37 +9393,37 @@
         <v>452.5</v>
       </c>
       <c r="M99">
-        <v>1583.813187</v>
+        <v>1600.141158</v>
       </c>
       <c r="N99">
-        <v>-1131.313187</v>
+        <v>-1147.641158</v>
       </c>
       <c r="O99">
-        <v>-282.82829675</v>
+        <v>-286.9102895</v>
       </c>
       <c r="P99">
-        <v>-848.48489025</v>
+        <v>-860.7308685</v>
       </c>
       <c r="Q99">
-        <v>-841.48489025</v>
+        <v>-853.7308685</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.291189115932798</v>
+        <v>1.913883673899197</v>
       </c>
       <c r="T99">
-        <v>17.14324995148373</v>
+        <v>25.7148749272256</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07142572175085697</v>
+        <v>0.07069688785544005</v>
       </c>
       <c r="W99">
-        <v>0.218957814811148</v>
+        <v>0.2191296738436873</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2857028870034279</v>
+        <v>0.2827875514217603</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2530247538447975</v>
+        <v>0.2549247538447975</v>
       </c>
       <c r="C100">
-        <v>-5173.356827692285</v>
+        <v>-5254.884979161245</v>
       </c>
       <c r="D100">
-        <v>1351.953172307715</v>
+        <v>1339.670020838755</v>
       </c>
       <c r="E100">
-        <v>94.3100000000004</v>
+        <v>163.5550000000003</v>
       </c>
       <c r="F100">
-        <v>6786.01</v>
+        <v>6855.255</v>
       </c>
       <c r="G100">
         <v>260.7</v>
@@ -9475,37 +9475,37 @@
         <v>452.5</v>
       </c>
       <c r="M100">
-        <v>1600.141158</v>
+        <v>1616.469129</v>
       </c>
       <c r="N100">
-        <v>-1147.641158</v>
+        <v>-1163.969129</v>
       </c>
       <c r="O100">
-        <v>-286.9102895</v>
+        <v>-290.99228225</v>
       </c>
       <c r="P100">
-        <v>-860.7308685</v>
+        <v>-872.97684675</v>
       </c>
       <c r="Q100">
-        <v>-853.7308685</v>
+        <v>-865.97684675</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.913883673899197</v>
+        <v>3.781967347798393</v>
       </c>
       <c r="T100">
-        <v>25.7148749272256</v>
+        <v>51.4297498544512</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07069688785544005</v>
+        <v>0.06998277787710228</v>
       </c>
       <c r="W100">
-        <v>0.2191296738436873</v>
+        <v>0.2192980609765793</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2827875514217603</v>
+        <v>0.2799311115084091</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2549247538447975</v>
-      </c>
-      <c r="C101">
-        <v>-5254.884979161245</v>
-      </c>
-      <c r="D101">
-        <v>1339.670020838755</v>
-      </c>
-      <c r="E101">
-        <v>163.5550000000003</v>
-      </c>
-      <c r="F101">
-        <v>6855.255</v>
-      </c>
-      <c r="G101">
-        <v>260.7</v>
-      </c>
-      <c r="H101">
-        <v>232.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>459.5</v>
-      </c>
-      <c r="K101">
-        <v>7</v>
-      </c>
-      <c r="L101">
-        <v>452.5</v>
-      </c>
-      <c r="M101">
-        <v>1616.469129</v>
-      </c>
-      <c r="N101">
-        <v>-1163.969129</v>
-      </c>
-      <c r="O101">
-        <v>-290.99228225</v>
-      </c>
-      <c r="P101">
-        <v>-872.97684675</v>
-      </c>
-      <c r="Q101">
-        <v>-865.97684675</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.781967347798393</v>
-      </c>
-      <c r="T101">
-        <v>51.4297498544512</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06998277787710228</v>
-      </c>
-      <c r="W101">
-        <v>0.2192980609765793</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2799311115084091</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
